--- a/La Liga 26-27.xlsx
+++ b/La Liga 26-27.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\La Liga 26-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E131D011-44EF-4CB6-A852-9E38FF6F5855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{399F04D9-834D-4D48-A049-5572ABACECA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="404" xr2:uid="{2BF33204-32E8-4B40-BC26-7C459B7DAA69}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="174">
   <si>
     <t>date</t>
   </si>
@@ -559,6 +559,9 @@
   <si>
     <t>Fri 18 September, 21:00</t>
   </si>
+  <si>
+    <t>Fri 9 October, 21:00</t>
+  </si>
 </sst>
 </file>
 
@@ -620,7 +623,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -646,6 +649,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -980,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886C5DDF-1A39-4E94-A421-1D1D9FD99BEC}">
-  <dimension ref="A1:CJ70"/>
+  <dimension ref="A1:CJ71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1310,7 +1314,7 @@
         <v>52</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H70" si="0">100-G2</f>
+        <f t="shared" ref="H2:H71" si="0">100-G2</f>
         <v>48</v>
       </c>
       <c r="I2">
@@ -19570,6 +19574,270 @@
       </c>
       <c r="CJ70">
         <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="2:88">
+      <c r="B71" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D71" t="s">
+        <v>95</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>58</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="I71">
+        <v>0.69</v>
+      </c>
+      <c r="J71">
+        <v>1.08</v>
+      </c>
+      <c r="K71">
+        <v>15</v>
+      </c>
+      <c r="L71">
+        <v>9</v>
+      </c>
+      <c r="M71">
+        <v>7</v>
+      </c>
+      <c r="N71">
+        <v>4</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>2</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>2</v>
+      </c>
+      <c r="S71">
+        <v>426</v>
+      </c>
+      <c r="T71">
+        <v>279</v>
+      </c>
+      <c r="U71">
+        <v>10</v>
+      </c>
+      <c r="V71">
+        <v>15</v>
+      </c>
+      <c r="W71">
+        <v>8</v>
+      </c>
+      <c r="X71">
+        <v>2</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA71">
+        <v>6</v>
+      </c>
+      <c r="AB71">
+        <v>2</v>
+      </c>
+      <c r="AC71">
+        <v>2</v>
+      </c>
+      <c r="AD71">
+        <v>3</v>
+      </c>
+      <c r="AE71">
+        <v>1</v>
+      </c>
+      <c r="AF71">
+        <v>0</v>
+      </c>
+      <c r="AG71">
+        <v>9</v>
+      </c>
+      <c r="AH71">
+        <v>6</v>
+      </c>
+      <c r="AI71">
+        <v>6</v>
+      </c>
+      <c r="AJ71">
+        <v>3</v>
+      </c>
+      <c r="AK71">
+        <v>0.39</v>
+      </c>
+      <c r="AL71">
+        <v>0.94</v>
+      </c>
+      <c r="AM71">
+        <v>0.3</v>
+      </c>
+      <c r="AN71">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AO71">
+        <v>0.69</v>
+      </c>
+      <c r="AP71">
+        <v>1.08</v>
+      </c>
+      <c r="AQ71">
+        <v>0.77</v>
+      </c>
+      <c r="AR71">
+        <v>0.82</v>
+      </c>
+      <c r="AS71">
+        <v>484</v>
+      </c>
+      <c r="AT71">
+        <v>353</v>
+      </c>
+      <c r="AU71">
+        <v>187</v>
+      </c>
+      <c r="AV71">
+        <v>196</v>
+      </c>
+      <c r="AW71">
+        <v>239</v>
+      </c>
+      <c r="AX71">
+        <v>83</v>
+      </c>
+      <c r="AY71">
+        <v>22</v>
+      </c>
+      <c r="AZ71">
+        <v>15</v>
+      </c>
+      <c r="BA71">
+        <v>6</v>
+      </c>
+      <c r="BB71">
+        <v>0</v>
+      </c>
+      <c r="BC71">
+        <v>24</v>
+      </c>
+      <c r="BD71">
+        <v>19</v>
+      </c>
+      <c r="BE71">
+        <v>37</v>
+      </c>
+      <c r="BF71">
+        <v>16</v>
+      </c>
+      <c r="BG71">
+        <v>2</v>
+      </c>
+      <c r="BH71">
+        <v>1</v>
+      </c>
+      <c r="BI71" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ71" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK71">
+        <v>15</v>
+      </c>
+      <c r="BL71">
+        <v>25</v>
+      </c>
+      <c r="BM71">
+        <v>7</v>
+      </c>
+      <c r="BN71">
+        <v>7</v>
+      </c>
+      <c r="BO71">
+        <v>4</v>
+      </c>
+      <c r="BP71">
+        <v>2</v>
+      </c>
+      <c r="BQ71">
+        <v>21</v>
+      </c>
+      <c r="BR71">
+        <v>27</v>
+      </c>
+      <c r="BS71">
+        <v>2</v>
+      </c>
+      <c r="BT71">
+        <v>6</v>
+      </c>
+      <c r="BU71" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV71" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW71">
+        <v>53</v>
+      </c>
+      <c r="BX71">
+        <v>55</v>
+      </c>
+      <c r="BY71">
+        <v>41</v>
+      </c>
+      <c r="BZ71">
+        <v>46</v>
+      </c>
+      <c r="CA71">
+        <v>12</v>
+      </c>
+      <c r="CB71">
+        <v>9</v>
+      </c>
+      <c r="CC71">
+        <v>12</v>
+      </c>
+      <c r="CD71">
+        <v>11</v>
+      </c>
+      <c r="CE71" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF71" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG71">
+        <v>4</v>
+      </c>
+      <c r="CH71">
+        <v>5</v>
+      </c>
+      <c r="CI71">
+        <v>0</v>
+      </c>
+      <c r="CJ71">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/La Liga 26-27.xlsx
+++ b/La Liga 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{399F04D9-834D-4D48-A049-5572ABACECA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E64FA2E-CD71-40A5-AFD8-C8ECFF123751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="404" xr2:uid="{2BF33204-32E8-4B40-BC26-7C459B7DAA69}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="177">
   <si>
     <t>date</t>
   </si>
@@ -562,6 +562,15 @@
   <si>
     <t>Fri 9 October, 21:00</t>
   </si>
+  <si>
+    <t>Sat 10 October, 16:15</t>
+  </si>
+  <si>
+    <t>Sat 10 October, 18:30</t>
+  </si>
+  <si>
+    <t>Sat 10 October, 21:00</t>
+  </si>
 </sst>
 </file>
 
@@ -984,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886C5DDF-1A39-4E94-A421-1D1D9FD99BEC}">
-  <dimension ref="A1:CJ71"/>
+  <dimension ref="A1:CJ74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1314,7 +1323,7 @@
         <v>52</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H71" si="0">100-G2</f>
+        <f t="shared" ref="H2:H74" si="0">100-G2</f>
         <v>48</v>
       </c>
       <c r="I2">
@@ -19837,6 +19846,798 @@
         <v>0</v>
       </c>
       <c r="CJ71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:88" ht="30">
+      <c r="B72" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72">
+        <v>32</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="I72">
+        <v>1.3</v>
+      </c>
+      <c r="J72">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K72">
+        <v>8</v>
+      </c>
+      <c r="L72">
+        <v>22</v>
+      </c>
+      <c r="M72">
+        <v>3</v>
+      </c>
+      <c r="N72">
+        <v>7</v>
+      </c>
+      <c r="O72">
+        <v>1</v>
+      </c>
+      <c r="P72">
+        <v>2</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>276</v>
+      </c>
+      <c r="T72">
+        <v>642</v>
+      </c>
+      <c r="U72">
+        <v>11</v>
+      </c>
+      <c r="V72">
+        <v>14</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>10</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA72">
+        <v>3</v>
+      </c>
+      <c r="AB72">
+        <v>4</v>
+      </c>
+      <c r="AC72">
+        <v>2</v>
+      </c>
+      <c r="AD72">
+        <v>11</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>1</v>
+      </c>
+      <c r="AG72">
+        <v>5</v>
+      </c>
+      <c r="AH72">
+        <v>11</v>
+      </c>
+      <c r="AI72">
+        <v>3</v>
+      </c>
+      <c r="AJ72">
+        <v>11</v>
+      </c>
+      <c r="AK72">
+        <v>0.5</v>
+      </c>
+      <c r="AL72">
+        <v>1.5</v>
+      </c>
+      <c r="AM72">
+        <v>0.01</v>
+      </c>
+      <c r="AN72">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AO72">
+        <v>0.51</v>
+      </c>
+      <c r="AP72">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="AQ72">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="AR72">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AS72">
+        <v>340</v>
+      </c>
+      <c r="AT72">
+        <v>706</v>
+      </c>
+      <c r="AU72">
+        <v>167</v>
+      </c>
+      <c r="AV72">
+        <v>269</v>
+      </c>
+      <c r="AW72">
+        <v>109</v>
+      </c>
+      <c r="AX72">
+        <v>373</v>
+      </c>
+      <c r="AY72">
+        <v>23</v>
+      </c>
+      <c r="AZ72">
+        <v>21</v>
+      </c>
+      <c r="BA72">
+        <v>1</v>
+      </c>
+      <c r="BB72">
+        <v>4</v>
+      </c>
+      <c r="BC72">
+        <v>14</v>
+      </c>
+      <c r="BD72">
+        <v>22</v>
+      </c>
+      <c r="BE72">
+        <v>7</v>
+      </c>
+      <c r="BF72">
+        <v>33</v>
+      </c>
+      <c r="BG72">
+        <v>1</v>
+      </c>
+      <c r="BH72">
+        <v>2</v>
+      </c>
+      <c r="BI72" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ72" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK72">
+        <v>21</v>
+      </c>
+      <c r="BL72">
+        <v>19</v>
+      </c>
+      <c r="BM72">
+        <v>15</v>
+      </c>
+      <c r="BN72">
+        <v>11</v>
+      </c>
+      <c r="BO72">
+        <v>10</v>
+      </c>
+      <c r="BP72">
+        <v>1</v>
+      </c>
+      <c r="BQ72">
+        <v>19</v>
+      </c>
+      <c r="BR72">
+        <v>10</v>
+      </c>
+      <c r="BS72">
+        <v>5</v>
+      </c>
+      <c r="BT72">
+        <v>2</v>
+      </c>
+      <c r="BU72" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV72" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW72">
+        <v>50</v>
+      </c>
+      <c r="BX72">
+        <v>53</v>
+      </c>
+      <c r="BY72">
+        <v>41</v>
+      </c>
+      <c r="BZ72">
+        <v>41</v>
+      </c>
+      <c r="CA72">
+        <v>9</v>
+      </c>
+      <c r="CB72">
+        <v>12</v>
+      </c>
+      <c r="CC72">
+        <v>8</v>
+      </c>
+      <c r="CD72">
+        <v>12</v>
+      </c>
+      <c r="CE72" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF72" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG72">
+        <v>0</v>
+      </c>
+      <c r="CH72">
+        <v>3</v>
+      </c>
+      <c r="CI72">
+        <v>1</v>
+      </c>
+      <c r="CJ72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:88" ht="25.5">
+      <c r="B73" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C73" t="s">
+        <v>119</v>
+      </c>
+      <c r="D73" t="s">
+        <v>88</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>83</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="I73">
+        <v>1.93</v>
+      </c>
+      <c r="J73">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K73">
+        <v>23</v>
+      </c>
+      <c r="L73">
+        <v>4</v>
+      </c>
+      <c r="M73">
+        <v>8</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73">
+        <v>5</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>4</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>783</v>
+      </c>
+      <c r="T73">
+        <v>108</v>
+      </c>
+      <c r="U73">
+        <v>9</v>
+      </c>
+      <c r="V73">
+        <v>11</v>
+      </c>
+      <c r="W73">
+        <v>9</v>
+      </c>
+      <c r="X73">
+        <v>2</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA73">
+        <v>6</v>
+      </c>
+      <c r="AB73">
+        <v>2</v>
+      </c>
+      <c r="AC73">
+        <v>9</v>
+      </c>
+      <c r="AD73">
+        <v>1</v>
+      </c>
+      <c r="AE73">
+        <v>0</v>
+      </c>
+      <c r="AF73">
+        <v>0</v>
+      </c>
+      <c r="AG73">
+        <v>16</v>
+      </c>
+      <c r="AH73">
+        <v>1</v>
+      </c>
+      <c r="AI73">
+        <v>7</v>
+      </c>
+      <c r="AJ73">
+        <v>3</v>
+      </c>
+      <c r="AK73">
+        <v>1.02</v>
+      </c>
+      <c r="AL73">
+        <v>0.11</v>
+      </c>
+      <c r="AM73">
+        <v>0.91</v>
+      </c>
+      <c r="AN73">
+        <v>0.03</v>
+      </c>
+      <c r="AO73">
+        <v>1.93</v>
+      </c>
+      <c r="AP73">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AQ73">
+        <v>1.7</v>
+      </c>
+      <c r="AR73">
+        <v>0.23</v>
+      </c>
+      <c r="AS73">
+        <v>858</v>
+      </c>
+      <c r="AT73">
+        <v>173</v>
+      </c>
+      <c r="AU73">
+        <v>220</v>
+      </c>
+      <c r="AV73">
+        <v>50</v>
+      </c>
+      <c r="AW73">
+        <v>563</v>
+      </c>
+      <c r="AX73">
+        <v>58</v>
+      </c>
+      <c r="AY73">
+        <v>26</v>
+      </c>
+      <c r="AZ73">
+        <v>22</v>
+      </c>
+      <c r="BA73">
+        <v>5</v>
+      </c>
+      <c r="BB73">
+        <v>1</v>
+      </c>
+      <c r="BC73">
+        <v>12</v>
+      </c>
+      <c r="BD73">
+        <v>11</v>
+      </c>
+      <c r="BE73">
+        <v>30</v>
+      </c>
+      <c r="BF73">
+        <v>3</v>
+      </c>
+      <c r="BG73">
+        <v>1</v>
+      </c>
+      <c r="BH73">
+        <v>3</v>
+      </c>
+      <c r="BI73" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ73" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK73">
+        <v>18</v>
+      </c>
+      <c r="BL73">
+        <v>12</v>
+      </c>
+      <c r="BM73">
+        <v>4</v>
+      </c>
+      <c r="BN73">
+        <v>9</v>
+      </c>
+      <c r="BO73">
+        <v>1</v>
+      </c>
+      <c r="BP73">
+        <v>9</v>
+      </c>
+      <c r="BQ73">
+        <v>13</v>
+      </c>
+      <c r="BR73">
+        <v>20</v>
+      </c>
+      <c r="BS73">
+        <v>1</v>
+      </c>
+      <c r="BT73">
+        <v>5</v>
+      </c>
+      <c r="BU73" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV73" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW73">
+        <v>54</v>
+      </c>
+      <c r="BX73">
+        <v>34</v>
+      </c>
+      <c r="BY73">
+        <v>41</v>
+      </c>
+      <c r="BZ73">
+        <v>27</v>
+      </c>
+      <c r="CA73">
+        <v>13</v>
+      </c>
+      <c r="CB73">
+        <v>7</v>
+      </c>
+      <c r="CC73">
+        <v>13</v>
+      </c>
+      <c r="CD73">
+        <v>6</v>
+      </c>
+      <c r="CE73" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF73" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG73">
+        <v>2</v>
+      </c>
+      <c r="CH73">
+        <v>4</v>
+      </c>
+      <c r="CI73">
+        <v>0</v>
+      </c>
+      <c r="CJ73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:88" ht="25.5">
+      <c r="B74" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D74" t="s">
+        <v>93</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>46</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I74">
+        <v>1.43</v>
+      </c>
+      <c r="J74">
+        <v>0.59</v>
+      </c>
+      <c r="K74">
+        <v>11</v>
+      </c>
+      <c r="L74">
+        <v>15</v>
+      </c>
+      <c r="M74">
+        <v>4</v>
+      </c>
+      <c r="N74">
+        <v>4</v>
+      </c>
+      <c r="O74">
+        <v>4</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>3</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>338</v>
+      </c>
+      <c r="T74">
+        <v>423</v>
+      </c>
+      <c r="U74">
+        <v>8</v>
+      </c>
+      <c r="V74">
+        <v>13</v>
+      </c>
+      <c r="W74">
+        <v>9</v>
+      </c>
+      <c r="X74">
+        <v>3</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA74">
+        <v>4</v>
+      </c>
+      <c r="AB74">
+        <v>7</v>
+      </c>
+      <c r="AC74">
+        <v>3</v>
+      </c>
+      <c r="AD74">
+        <v>4</v>
+      </c>
+      <c r="AE74">
+        <v>1</v>
+      </c>
+      <c r="AF74">
+        <v>0</v>
+      </c>
+      <c r="AG74">
+        <v>9</v>
+      </c>
+      <c r="AH74">
+        <v>7</v>
+      </c>
+      <c r="AI74">
+        <v>2</v>
+      </c>
+      <c r="AJ74">
+        <v>8</v>
+      </c>
+      <c r="AK74">
+        <v>1.38</v>
+      </c>
+      <c r="AL74">
+        <v>0.51</v>
+      </c>
+      <c r="AM74">
+        <v>0.05</v>
+      </c>
+      <c r="AN74">
+        <v>0.08</v>
+      </c>
+      <c r="AO74">
+        <v>1.43</v>
+      </c>
+      <c r="AP74">
+        <v>0.59</v>
+      </c>
+      <c r="AQ74">
+        <v>1.42</v>
+      </c>
+      <c r="AR74">
+        <v>1</v>
+      </c>
+      <c r="AS74">
+        <v>406</v>
+      </c>
+      <c r="AT74">
+        <v>478</v>
+      </c>
+      <c r="AU74">
+        <v>169</v>
+      </c>
+      <c r="AV74">
+        <v>209</v>
+      </c>
+      <c r="AW74">
+        <v>169</v>
+      </c>
+      <c r="AX74">
+        <v>214</v>
+      </c>
+      <c r="AY74">
+        <v>32</v>
+      </c>
+      <c r="AZ74">
+        <v>21</v>
+      </c>
+      <c r="BA74">
+        <v>2</v>
+      </c>
+      <c r="BB74">
+        <v>2</v>
+      </c>
+      <c r="BC74">
+        <v>21</v>
+      </c>
+      <c r="BD74">
+        <v>19</v>
+      </c>
+      <c r="BE74">
+        <v>30</v>
+      </c>
+      <c r="BF74">
+        <v>23</v>
+      </c>
+      <c r="BG74">
+        <v>3</v>
+      </c>
+      <c r="BH74">
+        <v>1</v>
+      </c>
+      <c r="BI74" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ74" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK74">
+        <v>19</v>
+      </c>
+      <c r="BL74">
+        <v>15</v>
+      </c>
+      <c r="BM74">
+        <v>5</v>
+      </c>
+      <c r="BN74">
+        <v>6</v>
+      </c>
+      <c r="BO74">
+        <v>3</v>
+      </c>
+      <c r="BP74">
+        <v>3</v>
+      </c>
+      <c r="BQ74">
+        <v>18</v>
+      </c>
+      <c r="BR74">
+        <v>25</v>
+      </c>
+      <c r="BS74">
+        <v>4</v>
+      </c>
+      <c r="BT74">
+        <v>3</v>
+      </c>
+      <c r="BU74" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV74" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW74">
+        <v>47</v>
+      </c>
+      <c r="BX74">
+        <v>35</v>
+      </c>
+      <c r="BY74">
+        <v>43</v>
+      </c>
+      <c r="BZ74">
+        <v>29</v>
+      </c>
+      <c r="CA74">
+        <v>4</v>
+      </c>
+      <c r="CB74">
+        <v>6</v>
+      </c>
+      <c r="CC74">
+        <v>11</v>
+      </c>
+      <c r="CD74">
+        <v>6</v>
+      </c>
+      <c r="CE74" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF74" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG74">
+        <v>5</v>
+      </c>
+      <c r="CH74">
+        <v>2</v>
+      </c>
+      <c r="CI74">
+        <v>1</v>
+      </c>
+      <c r="CJ74">
         <v>0</v>
       </c>
     </row>

--- a/La Liga 26-27.xlsx
+++ b/La Liga 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E64FA2E-CD71-40A5-AFD8-C8ECFF123751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B578007-8EC5-474A-8E9A-60AA83D24C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="404" xr2:uid="{2BF33204-32E8-4B40-BC26-7C459B7DAA69}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="183">
   <si>
     <t>date</t>
   </si>
@@ -571,6 +571,24 @@
   <si>
     <t>Sat 10 October, 21:00</t>
   </si>
+  <si>
+    <t>Sun 11 October, 14:00</t>
+  </si>
+  <si>
+    <t>Sun 11 October, 16:15</t>
+  </si>
+  <si>
+    <t>Sun 11 October, 18:30</t>
+  </si>
+  <si>
+    <t>Sun 11 October, 21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Mon 12 October, 21:00</t>
+  </si>
 </sst>
 </file>
 
@@ -658,7 +676,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -993,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886C5DDF-1A39-4E94-A421-1D1D9FD99BEC}">
-  <dimension ref="A1:CJ74"/>
+  <dimension ref="A1:CK79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1323,7 +1343,7 @@
         <v>52</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H74" si="0">100-G2</f>
+        <f t="shared" ref="H2:H79" si="0">100-G2</f>
         <v>48</v>
       </c>
       <c r="I2">
@@ -18001,7 +18021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:88" ht="25.5">
+    <row r="65" spans="2:89" ht="25.5">
       <c r="B65" s="2" t="s">
         <v>166</v>
       </c>
@@ -18265,7 +18285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:88" ht="25.5">
+    <row r="66" spans="2:89" ht="25.5">
       <c r="B66" s="2" t="s">
         <v>167</v>
       </c>
@@ -18529,7 +18549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:88" ht="25.5">
+    <row r="67" spans="2:89" ht="25.5">
       <c r="B67" s="2" t="s">
         <v>168</v>
       </c>
@@ -18793,7 +18813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="2:88" ht="30">
+    <row r="68" spans="2:89" ht="30">
       <c r="B68" s="2" t="s">
         <v>169</v>
       </c>
@@ -19057,7 +19077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:88" ht="25.5">
+    <row r="69" spans="2:89" ht="25.5">
       <c r="B69" s="2" t="s">
         <v>169</v>
       </c>
@@ -19321,7 +19341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:88" ht="25.5">
+    <row r="70" spans="2:89" ht="25.5">
       <c r="B70" s="2" t="s">
         <v>170</v>
       </c>
@@ -19585,7 +19605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="2:88">
+    <row r="71" spans="2:89">
       <c r="B71" s="9" t="s">
         <v>173</v>
       </c>
@@ -19849,7 +19869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:88" ht="30">
+    <row r="72" spans="2:89" ht="30">
       <c r="B72" s="2" t="s">
         <v>174</v>
       </c>
@@ -20113,7 +20133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:88" ht="25.5">
+    <row r="73" spans="2:89" ht="25.5">
       <c r="B73" s="2" t="s">
         <v>175</v>
       </c>
@@ -20377,7 +20397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:88" ht="25.5">
+    <row r="74" spans="2:89" ht="25.5">
       <c r="B74" s="2" t="s">
         <v>176</v>
       </c>
@@ -20639,6 +20659,1329 @@
       </c>
       <c r="CJ74">
         <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:89" ht="25.5">
+      <c r="B75" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C75" t="s">
+        <v>98</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>67</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="I75">
+        <v>0.78</v>
+      </c>
+      <c r="J75">
+        <v>0.47</v>
+      </c>
+      <c r="K75">
+        <v>13</v>
+      </c>
+      <c r="L75">
+        <v>7</v>
+      </c>
+      <c r="M75">
+        <v>2</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>1</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>1</v>
+      </c>
+      <c r="S75">
+        <v>597</v>
+      </c>
+      <c r="T75">
+        <v>280</v>
+      </c>
+      <c r="U75">
+        <v>19</v>
+      </c>
+      <c r="V75">
+        <v>21</v>
+      </c>
+      <c r="W75">
+        <v>5</v>
+      </c>
+      <c r="X75">
+        <v>2</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA75">
+        <v>7</v>
+      </c>
+      <c r="AB75">
+        <v>5</v>
+      </c>
+      <c r="AC75">
+        <v>4</v>
+      </c>
+      <c r="AD75">
+        <v>2</v>
+      </c>
+      <c r="AE75">
+        <v>1</v>
+      </c>
+      <c r="AF75">
+        <v>0</v>
+      </c>
+      <c r="AG75">
+        <v>8</v>
+      </c>
+      <c r="AH75">
+        <v>2</v>
+      </c>
+      <c r="AI75">
+        <v>5</v>
+      </c>
+      <c r="AJ75">
+        <v>5</v>
+      </c>
+      <c r="AK75">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AL75">
+        <v>0.45</v>
+      </c>
+      <c r="AM75">
+        <v>0.2</v>
+      </c>
+      <c r="AN75">
+        <v>0.02</v>
+      </c>
+      <c r="AO75">
+        <v>0.78</v>
+      </c>
+      <c r="AP75">
+        <v>0.47</v>
+      </c>
+      <c r="AQ75">
+        <v>0.42</v>
+      </c>
+      <c r="AR75">
+        <v>0</v>
+      </c>
+      <c r="AS75">
+        <v>653</v>
+      </c>
+      <c r="AT75">
+        <v>320</v>
+      </c>
+      <c r="AU75">
+        <v>312</v>
+      </c>
+      <c r="AV75">
+        <v>153</v>
+      </c>
+      <c r="AW75">
+        <v>285</v>
+      </c>
+      <c r="AX75">
+        <v>127</v>
+      </c>
+      <c r="AY75">
+        <v>40</v>
+      </c>
+      <c r="AZ75">
+        <v>10</v>
+      </c>
+      <c r="BA75">
+        <v>3</v>
+      </c>
+      <c r="BB75">
+        <v>2</v>
+      </c>
+      <c r="BC75">
+        <v>8</v>
+      </c>
+      <c r="BD75">
+        <v>9</v>
+      </c>
+      <c r="BE75">
+        <v>22</v>
+      </c>
+      <c r="BF75">
+        <v>10</v>
+      </c>
+      <c r="BG75">
+        <v>0</v>
+      </c>
+      <c r="BH75">
+        <v>3</v>
+      </c>
+      <c r="BI75" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ75" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK75">
+        <v>12</v>
+      </c>
+      <c r="BL75">
+        <v>18</v>
+      </c>
+      <c r="BM75">
+        <v>6</v>
+      </c>
+      <c r="BN75">
+        <v>7</v>
+      </c>
+      <c r="BO75">
+        <v>2</v>
+      </c>
+      <c r="BP75">
+        <v>4</v>
+      </c>
+      <c r="BQ75">
+        <v>4</v>
+      </c>
+      <c r="BR75">
+        <v>21</v>
+      </c>
+      <c r="BS75">
+        <v>0</v>
+      </c>
+      <c r="BT75">
+        <v>2</v>
+      </c>
+      <c r="BU75" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV75" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW75">
+        <v>46</v>
+      </c>
+      <c r="BX75">
+        <v>45</v>
+      </c>
+      <c r="BY75">
+        <v>39</v>
+      </c>
+      <c r="BZ75">
+        <v>39</v>
+      </c>
+      <c r="CA75">
+        <v>7</v>
+      </c>
+      <c r="CB75">
+        <v>6</v>
+      </c>
+      <c r="CC75">
+        <v>6</v>
+      </c>
+      <c r="CD75">
+        <v>3</v>
+      </c>
+      <c r="CE75" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF75" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG75">
+        <v>1</v>
+      </c>
+      <c r="CH75">
+        <v>3</v>
+      </c>
+      <c r="CI75">
+        <v>0</v>
+      </c>
+      <c r="CJ75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:89" ht="30">
+      <c r="B76" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76">
+        <v>40</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="I76">
+        <v>1.44</v>
+      </c>
+      <c r="J76">
+        <v>2.13</v>
+      </c>
+      <c r="K76">
+        <v>12</v>
+      </c>
+      <c r="L76">
+        <v>21</v>
+      </c>
+      <c r="M76">
+        <v>4</v>
+      </c>
+      <c r="N76">
+        <v>7</v>
+      </c>
+      <c r="O76">
+        <v>2</v>
+      </c>
+      <c r="P76">
+        <v>3</v>
+      </c>
+      <c r="Q76">
+        <v>1</v>
+      </c>
+      <c r="R76">
+        <v>2</v>
+      </c>
+      <c r="S76">
+        <v>285</v>
+      </c>
+      <c r="T76">
+        <v>443</v>
+      </c>
+      <c r="U76">
+        <v>14</v>
+      </c>
+      <c r="V76">
+        <v>13</v>
+      </c>
+      <c r="W76">
+        <v>7</v>
+      </c>
+      <c r="X76">
+        <v>10</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA76">
+        <v>4</v>
+      </c>
+      <c r="AB76">
+        <v>8</v>
+      </c>
+      <c r="AC76">
+        <v>4</v>
+      </c>
+      <c r="AD76">
+        <v>6</v>
+      </c>
+      <c r="AE76">
+        <v>0</v>
+      </c>
+      <c r="AF76">
+        <v>0</v>
+      </c>
+      <c r="AG76">
+        <v>6</v>
+      </c>
+      <c r="AH76">
+        <v>14</v>
+      </c>
+      <c r="AI76">
+        <v>6</v>
+      </c>
+      <c r="AJ76">
+        <v>7</v>
+      </c>
+      <c r="AK76">
+        <v>1.08</v>
+      </c>
+      <c r="AL76">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="AM76">
+        <v>0.35</v>
+      </c>
+      <c r="AN76">
+        <v>0.21</v>
+      </c>
+      <c r="AO76">
+        <v>1.44</v>
+      </c>
+      <c r="AP76">
+        <v>1.34</v>
+      </c>
+      <c r="AQ76">
+        <v>2.54</v>
+      </c>
+      <c r="AR76">
+        <v>1.55</v>
+      </c>
+      <c r="AS76">
+        <v>347</v>
+      </c>
+      <c r="AT76">
+        <v>515</v>
+      </c>
+      <c r="AU76">
+        <v>138</v>
+      </c>
+      <c r="AV76">
+        <v>172</v>
+      </c>
+      <c r="AW76">
+        <v>147</v>
+      </c>
+      <c r="AX76">
+        <v>271</v>
+      </c>
+      <c r="AY76">
+        <v>17</v>
+      </c>
+      <c r="AZ76">
+        <v>24</v>
+      </c>
+      <c r="BA76">
+        <v>2</v>
+      </c>
+      <c r="BB76">
+        <v>9</v>
+      </c>
+      <c r="BC76">
+        <v>13</v>
+      </c>
+      <c r="BD76">
+        <v>16</v>
+      </c>
+      <c r="BE76">
+        <v>11</v>
+      </c>
+      <c r="BF76">
+        <v>34</v>
+      </c>
+      <c r="BG76">
+        <v>4</v>
+      </c>
+      <c r="BH76">
+        <v>0</v>
+      </c>
+      <c r="BI76" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ76" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK76">
+        <v>18</v>
+      </c>
+      <c r="BL76">
+        <v>21</v>
+      </c>
+      <c r="BM76">
+        <v>11</v>
+      </c>
+      <c r="BN76">
+        <v>14</v>
+      </c>
+      <c r="BO76">
+        <v>6</v>
+      </c>
+      <c r="BP76">
+        <v>4</v>
+      </c>
+      <c r="BQ76">
+        <v>33</v>
+      </c>
+      <c r="BR76">
+        <v>16</v>
+      </c>
+      <c r="BS76">
+        <v>6</v>
+      </c>
+      <c r="BT76">
+        <v>1</v>
+      </c>
+      <c r="BU76" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV76" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW76">
+        <v>40</v>
+      </c>
+      <c r="BX76">
+        <v>64</v>
+      </c>
+      <c r="BY76">
+        <v>35</v>
+      </c>
+      <c r="BZ76">
+        <v>50</v>
+      </c>
+      <c r="CA76">
+        <v>5</v>
+      </c>
+      <c r="CB76">
+        <v>14</v>
+      </c>
+      <c r="CC76">
+        <v>6</v>
+      </c>
+      <c r="CD76">
+        <v>16</v>
+      </c>
+      <c r="CE76" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF76" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG76">
+        <v>1</v>
+      </c>
+      <c r="CH76">
+        <v>2</v>
+      </c>
+      <c r="CI76">
+        <v>1</v>
+      </c>
+      <c r="CJ76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="2:89" ht="25.5">
+      <c r="B77" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C77" t="s">
+        <v>101</v>
+      </c>
+      <c r="D77" t="s">
+        <v>121</v>
+      </c>
+      <c r="E77">
+        <v>5</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+      <c r="G77">
+        <v>52</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="I77">
+        <v>2.89</v>
+      </c>
+      <c r="J77">
+        <v>1.94</v>
+      </c>
+      <c r="K77">
+        <v>20</v>
+      </c>
+      <c r="L77">
+        <v>11</v>
+      </c>
+      <c r="M77">
+        <v>7</v>
+      </c>
+      <c r="N77">
+        <v>5</v>
+      </c>
+      <c r="O77">
+        <v>3</v>
+      </c>
+      <c r="P77">
+        <v>2</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>453</v>
+      </c>
+      <c r="T77">
+        <v>413</v>
+      </c>
+      <c r="U77">
+        <v>11</v>
+      </c>
+      <c r="V77">
+        <v>13</v>
+      </c>
+      <c r="W77">
+        <v>8</v>
+      </c>
+      <c r="X77">
+        <v>4</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA77">
+        <v>8</v>
+      </c>
+      <c r="AB77">
+        <v>2</v>
+      </c>
+      <c r="AC77">
+        <v>5</v>
+      </c>
+      <c r="AD77">
+        <v>4</v>
+      </c>
+      <c r="AE77">
+        <v>0</v>
+      </c>
+      <c r="AF77">
+        <v>0</v>
+      </c>
+      <c r="AG77">
+        <v>13</v>
+      </c>
+      <c r="AH77">
+        <v>6</v>
+      </c>
+      <c r="AI77">
+        <v>7</v>
+      </c>
+      <c r="AJ77">
+        <v>5</v>
+      </c>
+      <c r="AK77">
+        <v>2</v>
+      </c>
+      <c r="AL77">
+        <v>0.92</v>
+      </c>
+      <c r="AM77">
+        <v>0.1</v>
+      </c>
+      <c r="AN77">
+        <v>1.02</v>
+      </c>
+      <c r="AO77">
+        <v>2.1</v>
+      </c>
+      <c r="AP77">
+        <v>1.94</v>
+      </c>
+      <c r="AQ77">
+        <v>3.44</v>
+      </c>
+      <c r="AR77">
+        <v>2.23</v>
+      </c>
+      <c r="AS77">
+        <v>449</v>
+      </c>
+      <c r="AT77">
+        <v>466</v>
+      </c>
+      <c r="AU77">
+        <v>216</v>
+      </c>
+      <c r="AV77">
+        <v>213</v>
+      </c>
+      <c r="AW77">
+        <v>237</v>
+      </c>
+      <c r="AX77">
+        <v>200</v>
+      </c>
+      <c r="AY77">
+        <v>20</v>
+      </c>
+      <c r="AZ77">
+        <v>24</v>
+      </c>
+      <c r="BA77">
+        <v>6</v>
+      </c>
+      <c r="BB77">
+        <v>3</v>
+      </c>
+      <c r="BC77">
+        <v>17</v>
+      </c>
+      <c r="BD77">
+        <v>10</v>
+      </c>
+      <c r="BE77">
+        <v>32</v>
+      </c>
+      <c r="BF77">
+        <v>16</v>
+      </c>
+      <c r="BG77">
+        <v>0</v>
+      </c>
+      <c r="BH77">
+        <v>2</v>
+      </c>
+      <c r="BI77" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ77" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK77">
+        <v>15</v>
+      </c>
+      <c r="BL77">
+        <v>21</v>
+      </c>
+      <c r="BM77">
+        <v>8</v>
+      </c>
+      <c r="BN77">
+        <v>8</v>
+      </c>
+      <c r="BO77">
+        <v>4</v>
+      </c>
+      <c r="BP77">
+        <v>5</v>
+      </c>
+      <c r="BQ77">
+        <v>15</v>
+      </c>
+      <c r="BR77">
+        <v>31</v>
+      </c>
+      <c r="BS77">
+        <v>3</v>
+      </c>
+      <c r="BT77">
+        <v>3</v>
+      </c>
+      <c r="BU77" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV77" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW77">
+        <v>43</v>
+      </c>
+      <c r="BX77">
+        <v>52</v>
+      </c>
+      <c r="BY77">
+        <v>34</v>
+      </c>
+      <c r="BZ77">
+        <v>41</v>
+      </c>
+      <c r="CA77">
+        <v>9</v>
+      </c>
+      <c r="CB77">
+        <v>11</v>
+      </c>
+      <c r="CC77">
+        <v>6</v>
+      </c>
+      <c r="CD77">
+        <v>9</v>
+      </c>
+      <c r="CE77" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF77" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG77">
+        <v>2</v>
+      </c>
+      <c r="CH77">
+        <v>5</v>
+      </c>
+      <c r="CI77">
+        <v>0</v>
+      </c>
+      <c r="CJ77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:89" ht="30">
+      <c r="B78" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D78" t="s">
+        <v>112</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="F78">
+        <v>2</v>
+      </c>
+      <c r="G78">
+        <v>54</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="I78">
+        <v>1.28</v>
+      </c>
+      <c r="J78">
+        <v>1.8</v>
+      </c>
+      <c r="K78">
+        <v>20</v>
+      </c>
+      <c r="L78">
+        <v>10</v>
+      </c>
+      <c r="M78">
+        <v>11</v>
+      </c>
+      <c r="N78">
+        <v>2</v>
+      </c>
+      <c r="O78">
+        <v>1</v>
+      </c>
+      <c r="P78">
+        <v>5</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>3</v>
+      </c>
+      <c r="S78">
+        <v>446</v>
+      </c>
+      <c r="T78">
+        <v>351</v>
+      </c>
+      <c r="U78">
+        <v>15</v>
+      </c>
+      <c r="V78">
+        <v>10</v>
+      </c>
+      <c r="W78">
+        <v>8</v>
+      </c>
+      <c r="X78">
+        <v>3</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA78">
+        <v>5</v>
+      </c>
+      <c r="AB78">
+        <v>6</v>
+      </c>
+      <c r="AC78">
+        <v>4</v>
+      </c>
+      <c r="AD78">
+        <v>2</v>
+      </c>
+      <c r="AE78">
+        <v>0</v>
+      </c>
+      <c r="AF78">
+        <v>0</v>
+      </c>
+      <c r="AG78">
+        <v>7</v>
+      </c>
+      <c r="AH78">
+        <v>7</v>
+      </c>
+      <c r="AI78">
+        <v>13</v>
+      </c>
+      <c r="AJ78">
+        <v>3</v>
+      </c>
+      <c r="AK78">
+        <v>0.59</v>
+      </c>
+      <c r="AL78">
+        <v>1.65</v>
+      </c>
+      <c r="AM78">
+        <v>0.69</v>
+      </c>
+      <c r="AN78">
+        <v>0.15</v>
+      </c>
+      <c r="AO78">
+        <v>1.28</v>
+      </c>
+      <c r="AP78">
+        <v>1.8</v>
+      </c>
+      <c r="AQ78">
+        <v>2.29</v>
+      </c>
+      <c r="AR78">
+        <v>1.35</v>
+      </c>
+      <c r="AS78">
+        <v>524</v>
+      </c>
+      <c r="AT78">
+        <v>453</v>
+      </c>
+      <c r="AU78">
+        <v>164</v>
+      </c>
+      <c r="AV78">
+        <v>225</v>
+      </c>
+      <c r="AW78">
+        <v>282</v>
+      </c>
+      <c r="AX78">
+        <v>126</v>
+      </c>
+      <c r="AY78">
+        <v>11</v>
+      </c>
+      <c r="AZ78">
+        <v>31</v>
+      </c>
+      <c r="BA78">
+        <v>2</v>
+      </c>
+      <c r="BB78">
+        <v>5</v>
+      </c>
+      <c r="BC78">
+        <v>19</v>
+      </c>
+      <c r="BD78">
+        <v>12</v>
+      </c>
+      <c r="BE78">
+        <v>30</v>
+      </c>
+      <c r="BF78">
+        <v>13</v>
+      </c>
+      <c r="BG78">
+        <v>1</v>
+      </c>
+      <c r="BH78">
+        <v>1</v>
+      </c>
+      <c r="BI78" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ78" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK78">
+        <v>15</v>
+      </c>
+      <c r="BL78">
+        <v>15</v>
+      </c>
+      <c r="BM78">
+        <v>10</v>
+      </c>
+      <c r="BN78">
+        <v>11</v>
+      </c>
+      <c r="BO78">
+        <v>2</v>
+      </c>
+      <c r="BP78">
+        <v>3</v>
+      </c>
+      <c r="BQ78">
+        <v>9</v>
+      </c>
+      <c r="BR78">
+        <v>37</v>
+      </c>
+      <c r="BS78">
+        <v>0</v>
+      </c>
+      <c r="BT78">
+        <v>9</v>
+      </c>
+      <c r="BU78" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV78" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW78">
+        <v>47</v>
+      </c>
+      <c r="BX78">
+        <v>58</v>
+      </c>
+      <c r="BY78">
+        <v>32</v>
+      </c>
+      <c r="BZ78">
+        <v>45</v>
+      </c>
+      <c r="CA78">
+        <v>15</v>
+      </c>
+      <c r="CB78">
+        <v>13</v>
+      </c>
+      <c r="CC78">
+        <v>8</v>
+      </c>
+      <c r="CD78">
+        <v>15</v>
+      </c>
+      <c r="CE78" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF78" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG78">
+        <v>3</v>
+      </c>
+      <c r="CH78">
+        <v>3</v>
+      </c>
+      <c r="CI78">
+        <v>0</v>
+      </c>
+      <c r="CJ78">
+        <v>0</v>
+      </c>
+      <c r="CK78" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="79" spans="2:89" ht="25.5">
+      <c r="B79" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C79" t="s">
+        <v>96</v>
+      </c>
+      <c r="D79" t="s">
+        <v>90</v>
+      </c>
+      <c r="E79">
+        <v>3</v>
+      </c>
+      <c r="F79">
+        <v>3</v>
+      </c>
+      <c r="G79">
+        <v>57</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="I79">
+        <v>1.95</v>
+      </c>
+      <c r="J79">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="K79">
+        <v>20</v>
+      </c>
+      <c r="L79">
+        <v>18</v>
+      </c>
+      <c r="M79">
+        <v>8</v>
+      </c>
+      <c r="N79">
+        <v>5</v>
+      </c>
+      <c r="O79">
+        <v>3</v>
+      </c>
+      <c r="P79">
+        <v>5</v>
+      </c>
+      <c r="Q79">
+        <v>2</v>
+      </c>
+      <c r="R79">
+        <v>3</v>
+      </c>
+      <c r="S79">
+        <v>409</v>
+      </c>
+      <c r="T79">
+        <v>305</v>
+      </c>
+      <c r="U79">
+        <v>7</v>
+      </c>
+      <c r="V79">
+        <v>17</v>
+      </c>
+      <c r="W79">
+        <v>5</v>
+      </c>
+      <c r="X79">
+        <v>2</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA79">
+        <v>7</v>
+      </c>
+      <c r="AB79">
+        <v>8</v>
+      </c>
+      <c r="AC79">
+        <v>5</v>
+      </c>
+      <c r="AD79">
+        <v>5</v>
+      </c>
+      <c r="AE79">
+        <v>0</v>
+      </c>
+      <c r="AF79">
+        <v>1</v>
+      </c>
+      <c r="AG79">
+        <v>12</v>
+      </c>
+      <c r="AH79">
+        <v>14</v>
+      </c>
+      <c r="AI79">
+        <v>8</v>
+      </c>
+      <c r="AJ79">
+        <v>4</v>
+      </c>
+      <c r="AK79">
+        <v>1.47</v>
+      </c>
+      <c r="AL79">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="AM79">
+        <v>0.48</v>
+      </c>
+      <c r="AN79">
+        <v>0.06</v>
+      </c>
+      <c r="AO79">
+        <v>1.95</v>
+      </c>
+      <c r="AP79">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="AQ79">
+        <v>3.15</v>
+      </c>
+      <c r="AR79">
+        <v>2.61</v>
+      </c>
+      <c r="AS79">
+        <v>506</v>
+      </c>
+      <c r="AT79">
+        <v>385</v>
+      </c>
+      <c r="AU79">
+        <v>252</v>
+      </c>
+      <c r="AV79">
+        <v>154</v>
+      </c>
+      <c r="AW79">
+        <v>159</v>
+      </c>
+      <c r="AX79">
+        <v>151</v>
+      </c>
+      <c r="AY79">
+        <v>28</v>
+      </c>
+      <c r="AZ79">
+        <v>34</v>
+      </c>
+      <c r="BA79">
+        <v>6</v>
+      </c>
+      <c r="BB79">
+        <v>1</v>
+      </c>
+      <c r="BC79">
+        <v>26</v>
+      </c>
+      <c r="BD79">
+        <v>15</v>
+      </c>
+      <c r="BE79">
+        <v>27</v>
+      </c>
+      <c r="BF79">
+        <v>27</v>
+      </c>
+      <c r="BG79">
+        <v>0</v>
+      </c>
+      <c r="BH79">
+        <v>0</v>
+      </c>
+      <c r="BI79" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ79" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK79">
+        <v>19</v>
+      </c>
+      <c r="BL79">
+        <v>23</v>
+      </c>
+      <c r="BM79">
+        <v>6</v>
+      </c>
+      <c r="BN79">
+        <v>9</v>
+      </c>
+      <c r="BO79">
+        <v>5</v>
+      </c>
+      <c r="BP79">
+        <v>4</v>
+      </c>
+      <c r="BQ79">
+        <v>16</v>
+      </c>
+      <c r="BR79">
+        <v>35</v>
+      </c>
+      <c r="BS79">
+        <v>2</v>
+      </c>
+      <c r="BT79">
+        <v>5</v>
+      </c>
+      <c r="BU79" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV79" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW79">
+        <v>59</v>
+      </c>
+      <c r="BX79">
+        <v>63</v>
+      </c>
+      <c r="BY79">
+        <v>42</v>
+      </c>
+      <c r="BZ79">
+        <v>40</v>
+      </c>
+      <c r="CA79">
+        <v>17</v>
+      </c>
+      <c r="CB79">
+        <v>23</v>
+      </c>
+      <c r="CC79">
+        <v>9</v>
+      </c>
+      <c r="CD79">
+        <v>10</v>
+      </c>
+      <c r="CE79" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF79" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG79">
+        <v>2</v>
+      </c>
+      <c r="CH79">
+        <v>4</v>
+      </c>
+      <c r="CI79">
+        <v>0</v>
+      </c>
+      <c r="CJ79">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/La Liga 26-27.xlsx
+++ b/La Liga 26-27.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B578007-8EC5-474A-8E9A-60AA83D24C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2746546C-AF81-43E8-AF06-F2E452289312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="404" xr2:uid="{2BF33204-32E8-4B40-BC26-7C459B7DAA69}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="184">
   <si>
     <t>date</t>
   </si>
@@ -589,6 +589,9 @@
   <si>
     <t>Mon 12 October, 21:00</t>
   </si>
+  <si>
+    <t>Fri 16 October, 21:00</t>
+  </si>
 </sst>
 </file>
 
@@ -1013,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886C5DDF-1A39-4E94-A421-1D1D9FD99BEC}">
-  <dimension ref="A1:CK79"/>
+  <dimension ref="A1:CK80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1343,7 +1346,7 @@
         <v>52</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H79" si="0">100-G2</f>
+        <f t="shared" ref="H2:H80" si="0">100-G2</f>
         <v>48</v>
       </c>
       <c r="I2">
@@ -21982,6 +21985,270 @@
       </c>
       <c r="CJ79">
         <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="2:89" ht="30">
+      <c r="B80" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D80" t="s">
+        <v>96</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80">
+        <v>46</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="I80">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="J80">
+        <v>0.83</v>
+      </c>
+      <c r="K80">
+        <v>13</v>
+      </c>
+      <c r="L80">
+        <v>11</v>
+      </c>
+      <c r="M80">
+        <v>5</v>
+      </c>
+      <c r="N80">
+        <v>3</v>
+      </c>
+      <c r="O80">
+        <v>2</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>1</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>305</v>
+      </c>
+      <c r="T80">
+        <v>344</v>
+      </c>
+      <c r="U80">
+        <v>17</v>
+      </c>
+      <c r="V80">
+        <v>12</v>
+      </c>
+      <c r="W80">
+        <v>3</v>
+      </c>
+      <c r="X80">
+        <v>5</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA80">
+        <v>4</v>
+      </c>
+      <c r="AB80">
+        <v>6</v>
+      </c>
+      <c r="AC80">
+        <v>4</v>
+      </c>
+      <c r="AD80">
+        <v>1</v>
+      </c>
+      <c r="AE80">
+        <v>1</v>
+      </c>
+      <c r="AF80">
+        <v>0</v>
+      </c>
+      <c r="AG80">
+        <v>9</v>
+      </c>
+      <c r="AH80">
+        <v>6</v>
+      </c>
+      <c r="AI80">
+        <v>4</v>
+      </c>
+      <c r="AJ80">
+        <v>5</v>
+      </c>
+      <c r="AK80">
+        <v>1.08</v>
+      </c>
+      <c r="AL80">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AM80">
+        <v>0.03</v>
+      </c>
+      <c r="AN80">
+        <v>0.27</v>
+      </c>
+      <c r="AO80">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AP80">
+        <v>0.83</v>
+      </c>
+      <c r="AQ80">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AR80">
+        <v>1.06</v>
+      </c>
+      <c r="AS80">
+        <v>374</v>
+      </c>
+      <c r="AT80">
+        <v>423</v>
+      </c>
+      <c r="AU80">
+        <v>167</v>
+      </c>
+      <c r="AV80">
+        <v>198</v>
+      </c>
+      <c r="AW80">
+        <v>138</v>
+      </c>
+      <c r="AX80">
+        <v>146</v>
+      </c>
+      <c r="AY80">
+        <v>24</v>
+      </c>
+      <c r="AZ80">
+        <v>29</v>
+      </c>
+      <c r="BA80">
+        <v>2</v>
+      </c>
+      <c r="BB80">
+        <v>6</v>
+      </c>
+      <c r="BC80">
+        <v>23</v>
+      </c>
+      <c r="BD80">
+        <v>22</v>
+      </c>
+      <c r="BE80">
+        <v>15</v>
+      </c>
+      <c r="BF80">
+        <v>21</v>
+      </c>
+      <c r="BG80">
+        <v>1</v>
+      </c>
+      <c r="BH80">
+        <v>0</v>
+      </c>
+      <c r="BI80" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ80" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK80">
+        <v>8</v>
+      </c>
+      <c r="BL80">
+        <v>16</v>
+      </c>
+      <c r="BM80">
+        <v>3</v>
+      </c>
+      <c r="BN80">
+        <v>6</v>
+      </c>
+      <c r="BO80">
+        <v>1</v>
+      </c>
+      <c r="BP80">
+        <v>4</v>
+      </c>
+      <c r="BQ80">
+        <v>28</v>
+      </c>
+      <c r="BR80">
+        <v>19</v>
+      </c>
+      <c r="BS80">
+        <v>3</v>
+      </c>
+      <c r="BT80">
+        <v>4</v>
+      </c>
+      <c r="BU80" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV80" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW80">
+        <v>43</v>
+      </c>
+      <c r="BX80">
+        <v>48</v>
+      </c>
+      <c r="BY80">
+        <v>27</v>
+      </c>
+      <c r="BZ80">
+        <v>37</v>
+      </c>
+      <c r="CA80">
+        <v>16</v>
+      </c>
+      <c r="CB80">
+        <v>11</v>
+      </c>
+      <c r="CC80">
+        <v>8</v>
+      </c>
+      <c r="CD80">
+        <v>5</v>
+      </c>
+      <c r="CE80" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF80" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG80">
+        <v>3</v>
+      </c>
+      <c r="CH80">
+        <v>2</v>
+      </c>
+      <c r="CI80">
+        <v>0</v>
+      </c>
+      <c r="CJ80">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/La Liga 26-27.xlsx
+++ b/La Liga 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2746546C-AF81-43E8-AF06-F2E452289312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8A07AFD-203A-4FAB-B9F2-B5DCF16B621A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="404" xr2:uid="{2BF33204-32E8-4B40-BC26-7C459B7DAA69}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="191">
   <si>
     <t>date</t>
   </si>
@@ -592,6 +592,27 @@
   <si>
     <t>Fri 16 October, 21:00</t>
   </si>
+  <si>
+    <t>Sat 17 October, 14:00</t>
+  </si>
+  <si>
+    <t>Sat 17 October, 16:15</t>
+  </si>
+  <si>
+    <t>Sat 17 October, 18:30</t>
+  </si>
+  <si>
+    <t>Sat 17 October, 21:00</t>
+  </si>
+  <si>
+    <t>Sun 18 October, 14:00</t>
+  </si>
+  <si>
+    <t>Sun 18 October, 16:15</t>
+  </si>
+  <si>
+    <t>Sun 18 October, 18:30</t>
+  </si>
 </sst>
 </file>
 
@@ -1016,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886C5DDF-1A39-4E94-A421-1D1D9FD99BEC}">
-  <dimension ref="A1:CK80"/>
+  <dimension ref="A1:CK87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1346,7 +1367,7 @@
         <v>52</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H80" si="0">100-G2</f>
+        <f t="shared" ref="H2:H87" si="0">100-G2</f>
         <v>48</v>
       </c>
       <c r="I2">
@@ -22248,6 +22269,1854 @@
         <v>0</v>
       </c>
       <c r="CJ80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:88" ht="30">
+      <c r="B81" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C81" t="s">
+        <v>95</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>30</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="I81">
+        <v>0.51</v>
+      </c>
+      <c r="J81">
+        <v>1.47</v>
+      </c>
+      <c r="K81">
+        <v>10</v>
+      </c>
+      <c r="L81">
+        <v>19</v>
+      </c>
+      <c r="M81">
+        <v>2</v>
+      </c>
+      <c r="N81">
+        <v>6</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>3</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <v>3</v>
+      </c>
+      <c r="S81">
+        <v>198</v>
+      </c>
+      <c r="T81">
+        <v>600</v>
+      </c>
+      <c r="U81">
+        <v>10</v>
+      </c>
+      <c r="V81">
+        <v>9</v>
+      </c>
+      <c r="W81">
+        <v>4</v>
+      </c>
+      <c r="X81">
+        <v>12</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA81">
+        <v>5</v>
+      </c>
+      <c r="AB81">
+        <v>9</v>
+      </c>
+      <c r="AC81">
+        <v>3</v>
+      </c>
+      <c r="AD81">
+        <v>4</v>
+      </c>
+      <c r="AE81">
+        <v>1</v>
+      </c>
+      <c r="AF81">
+        <v>1</v>
+      </c>
+      <c r="AG81">
+        <v>6</v>
+      </c>
+      <c r="AH81">
+        <v>10</v>
+      </c>
+      <c r="AI81">
+        <v>4</v>
+      </c>
+      <c r="AJ81">
+        <v>9</v>
+      </c>
+      <c r="AK81">
+        <v>0.16</v>
+      </c>
+      <c r="AL81">
+        <v>1.3</v>
+      </c>
+      <c r="AM81">
+        <v>0.36</v>
+      </c>
+      <c r="AN81">
+        <v>0.17</v>
+      </c>
+      <c r="AO81">
+        <v>0.51</v>
+      </c>
+      <c r="AP81">
+        <v>1.47</v>
+      </c>
+      <c r="AQ81">
+        <v>0.62</v>
+      </c>
+      <c r="AR81">
+        <v>1.7</v>
+      </c>
+      <c r="AS81">
+        <v>273</v>
+      </c>
+      <c r="AT81">
+        <v>670</v>
+      </c>
+      <c r="AU81">
+        <v>125</v>
+      </c>
+      <c r="AV81">
+        <v>294</v>
+      </c>
+      <c r="AW81">
+        <v>73</v>
+      </c>
+      <c r="AX81">
+        <v>306</v>
+      </c>
+      <c r="AY81">
+        <v>21</v>
+      </c>
+      <c r="AZ81">
+        <v>22</v>
+      </c>
+      <c r="BA81">
+        <v>3</v>
+      </c>
+      <c r="BB81">
+        <v>6</v>
+      </c>
+      <c r="BC81">
+        <v>15</v>
+      </c>
+      <c r="BD81">
+        <v>14</v>
+      </c>
+      <c r="BE81">
+        <v>11</v>
+      </c>
+      <c r="BF81">
+        <v>24</v>
+      </c>
+      <c r="BG81">
+        <v>0</v>
+      </c>
+      <c r="BH81">
+        <v>4</v>
+      </c>
+      <c r="BI81" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ81" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK81">
+        <v>11</v>
+      </c>
+      <c r="BL81">
+        <v>11</v>
+      </c>
+      <c r="BM81">
+        <v>11</v>
+      </c>
+      <c r="BN81">
+        <v>10</v>
+      </c>
+      <c r="BO81">
+        <v>4</v>
+      </c>
+      <c r="BP81">
+        <v>3</v>
+      </c>
+      <c r="BQ81">
+        <v>17</v>
+      </c>
+      <c r="BR81">
+        <v>18</v>
+      </c>
+      <c r="BS81">
+        <v>5</v>
+      </c>
+      <c r="BT81">
+        <v>2</v>
+      </c>
+      <c r="BU81" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV81" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW81">
+        <v>34</v>
+      </c>
+      <c r="BX81">
+        <v>50</v>
+      </c>
+      <c r="BY81">
+        <v>24</v>
+      </c>
+      <c r="BZ81">
+        <v>29</v>
+      </c>
+      <c r="CA81">
+        <v>10</v>
+      </c>
+      <c r="CB81">
+        <v>21</v>
+      </c>
+      <c r="CC81">
+        <v>5</v>
+      </c>
+      <c r="CD81">
+        <v>8</v>
+      </c>
+      <c r="CE81" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF81" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG81">
+        <v>2</v>
+      </c>
+      <c r="CH81">
+        <v>5</v>
+      </c>
+      <c r="CI81">
+        <v>0</v>
+      </c>
+      <c r="CJ81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:88" ht="25.5">
+      <c r="B82" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C82" t="s">
+        <v>93</v>
+      </c>
+      <c r="D82" t="s">
+        <v>98</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>58</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="I82">
+        <v>2.38</v>
+      </c>
+      <c r="J82">
+        <v>0.3</v>
+      </c>
+      <c r="K82">
+        <v>20</v>
+      </c>
+      <c r="L82">
+        <v>7</v>
+      </c>
+      <c r="M82">
+        <v>7</v>
+      </c>
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82">
+        <v>4</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>4</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>460</v>
+      </c>
+      <c r="T82">
+        <v>308</v>
+      </c>
+      <c r="U82">
+        <v>12</v>
+      </c>
+      <c r="V82">
+        <v>7</v>
+      </c>
+      <c r="W82">
+        <v>10</v>
+      </c>
+      <c r="X82">
+        <v>5</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA82">
+        <v>5</v>
+      </c>
+      <c r="AB82">
+        <v>5</v>
+      </c>
+      <c r="AC82">
+        <v>8</v>
+      </c>
+      <c r="AD82">
+        <v>1</v>
+      </c>
+      <c r="AE82">
+        <v>0</v>
+      </c>
+      <c r="AF82">
+        <v>0</v>
+      </c>
+      <c r="AG82">
+        <v>16</v>
+      </c>
+      <c r="AH82">
+        <v>1</v>
+      </c>
+      <c r="AI82">
+        <v>4</v>
+      </c>
+      <c r="AJ82">
+        <v>6</v>
+      </c>
+      <c r="AK82">
+        <v>2.11</v>
+      </c>
+      <c r="AL82">
+        <v>0.22</v>
+      </c>
+      <c r="AM82">
+        <v>0.27</v>
+      </c>
+      <c r="AN82">
+        <v>0.09</v>
+      </c>
+      <c r="AO82">
+        <v>2.38</v>
+      </c>
+      <c r="AP82">
+        <v>0.3</v>
+      </c>
+      <c r="AQ82">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="AR82">
+        <v>0.25</v>
+      </c>
+      <c r="AS82">
+        <v>529</v>
+      </c>
+      <c r="AT82">
+        <v>388</v>
+      </c>
+      <c r="AU82">
+        <v>214</v>
+      </c>
+      <c r="AV82">
+        <v>210</v>
+      </c>
+      <c r="AW82">
+        <v>246</v>
+      </c>
+      <c r="AX82">
+        <v>98</v>
+      </c>
+      <c r="AY82">
+        <v>27</v>
+      </c>
+      <c r="AZ82">
+        <v>24</v>
+      </c>
+      <c r="BA82">
+        <v>7</v>
+      </c>
+      <c r="BB82">
+        <v>2</v>
+      </c>
+      <c r="BC82">
+        <v>11</v>
+      </c>
+      <c r="BD82">
+        <v>16</v>
+      </c>
+      <c r="BE82">
+        <v>46</v>
+      </c>
+      <c r="BF82">
+        <v>11</v>
+      </c>
+      <c r="BG82">
+        <v>6</v>
+      </c>
+      <c r="BH82">
+        <v>0</v>
+      </c>
+      <c r="BI82" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ82" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK82">
+        <v>11</v>
+      </c>
+      <c r="BL82">
+        <v>16</v>
+      </c>
+      <c r="BM82">
+        <v>8</v>
+      </c>
+      <c r="BN82">
+        <v>8</v>
+      </c>
+      <c r="BO82">
+        <v>1</v>
+      </c>
+      <c r="BP82">
+        <v>8</v>
+      </c>
+      <c r="BQ82">
+        <v>8</v>
+      </c>
+      <c r="BR82">
+        <v>25</v>
+      </c>
+      <c r="BS82">
+        <v>1</v>
+      </c>
+      <c r="BT82">
+        <v>6</v>
+      </c>
+      <c r="BU82" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV82" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW82">
+        <v>36</v>
+      </c>
+      <c r="BX82">
+        <v>39</v>
+      </c>
+      <c r="BY82">
+        <v>28</v>
+      </c>
+      <c r="BZ82">
+        <v>34</v>
+      </c>
+      <c r="CA82">
+        <v>8</v>
+      </c>
+      <c r="CB82">
+        <v>5</v>
+      </c>
+      <c r="CC82">
+        <v>11</v>
+      </c>
+      <c r="CD82">
+        <v>7</v>
+      </c>
+      <c r="CE82" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF82" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG82">
+        <v>2</v>
+      </c>
+      <c r="CH82">
+        <v>4</v>
+      </c>
+      <c r="CI82">
+        <v>0</v>
+      </c>
+      <c r="CJ82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:88" ht="25.5">
+      <c r="B83" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C83" t="s">
+        <v>101</v>
+      </c>
+      <c r="D83" t="s">
+        <v>119</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="F83">
+        <v>5</v>
+      </c>
+      <c r="G83">
+        <v>31</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="I83">
+        <v>1.24</v>
+      </c>
+      <c r="J83">
+        <v>3.1</v>
+      </c>
+      <c r="K83">
+        <v>6</v>
+      </c>
+      <c r="L83">
+        <v>18</v>
+      </c>
+      <c r="M83">
+        <v>5</v>
+      </c>
+      <c r="N83">
+        <v>10</v>
+      </c>
+      <c r="O83">
+        <v>3</v>
+      </c>
+      <c r="P83">
+        <v>5</v>
+      </c>
+      <c r="Q83">
+        <v>1</v>
+      </c>
+      <c r="R83">
+        <v>2</v>
+      </c>
+      <c r="S83">
+        <v>256</v>
+      </c>
+      <c r="T83">
+        <v>692</v>
+      </c>
+      <c r="U83">
+        <v>10</v>
+      </c>
+      <c r="V83">
+        <v>11</v>
+      </c>
+      <c r="W83">
+        <v>2</v>
+      </c>
+      <c r="X83">
+        <v>5</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA83">
+        <v>0</v>
+      </c>
+      <c r="AB83">
+        <v>6</v>
+      </c>
+      <c r="AC83">
+        <v>1</v>
+      </c>
+      <c r="AD83">
+        <v>2</v>
+      </c>
+      <c r="AE83">
+        <v>0</v>
+      </c>
+      <c r="AF83">
+        <v>0</v>
+      </c>
+      <c r="AG83">
+        <v>3</v>
+      </c>
+      <c r="AH83">
+        <v>8</v>
+      </c>
+      <c r="AI83">
+        <v>3</v>
+      </c>
+      <c r="AJ83">
+        <v>10</v>
+      </c>
+      <c r="AK83">
+        <v>0.98</v>
+      </c>
+      <c r="AL83">
+        <v>1.93</v>
+      </c>
+      <c r="AM83">
+        <v>0.26</v>
+      </c>
+      <c r="AN83">
+        <v>1.17</v>
+      </c>
+      <c r="AO83">
+        <v>1.24</v>
+      </c>
+      <c r="AP83">
+        <v>3.1</v>
+      </c>
+      <c r="AQ83">
+        <v>1.9</v>
+      </c>
+      <c r="AR83">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AS83">
+        <v>324</v>
+      </c>
+      <c r="AT83">
+        <v>751</v>
+      </c>
+      <c r="AU83">
+        <v>162</v>
+      </c>
+      <c r="AV83">
+        <v>299</v>
+      </c>
+      <c r="AW83">
+        <v>94</v>
+      </c>
+      <c r="AX83">
+        <v>393</v>
+      </c>
+      <c r="AY83">
+        <v>28</v>
+      </c>
+      <c r="AZ83">
+        <v>19</v>
+      </c>
+      <c r="BA83">
+        <v>2</v>
+      </c>
+      <c r="BB83">
+        <v>1</v>
+      </c>
+      <c r="BC83">
+        <v>20</v>
+      </c>
+      <c r="BD83">
+        <v>23</v>
+      </c>
+      <c r="BE83">
+        <v>11</v>
+      </c>
+      <c r="BF83">
+        <v>31</v>
+      </c>
+      <c r="BG83">
+        <v>1</v>
+      </c>
+      <c r="BH83">
+        <v>2</v>
+      </c>
+      <c r="BI83" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ83" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK83">
+        <v>17</v>
+      </c>
+      <c r="BL83">
+        <v>15</v>
+      </c>
+      <c r="BM83">
+        <v>14</v>
+      </c>
+      <c r="BN83">
+        <v>6</v>
+      </c>
+      <c r="BO83">
+        <v>2</v>
+      </c>
+      <c r="BP83">
+        <v>1</v>
+      </c>
+      <c r="BQ83">
+        <v>20</v>
+      </c>
+      <c r="BR83">
+        <v>17</v>
+      </c>
+      <c r="BS83">
+        <v>5</v>
+      </c>
+      <c r="BT83">
+        <v>3</v>
+      </c>
+      <c r="BU83" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV83" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW83">
+        <v>38</v>
+      </c>
+      <c r="BX83">
+        <v>45</v>
+      </c>
+      <c r="BY83">
+        <v>33</v>
+      </c>
+      <c r="BZ83">
+        <v>35</v>
+      </c>
+      <c r="CA83">
+        <v>5</v>
+      </c>
+      <c r="CB83">
+        <v>10</v>
+      </c>
+      <c r="CC83">
+        <v>6</v>
+      </c>
+      <c r="CD83">
+        <v>12</v>
+      </c>
+      <c r="CE83" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF83" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG83">
+        <v>3</v>
+      </c>
+      <c r="CH83">
+        <v>2</v>
+      </c>
+      <c r="CI83">
+        <v>1</v>
+      </c>
+      <c r="CJ83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:88" ht="25.5">
+      <c r="B84" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C84" t="s">
+        <v>112</v>
+      </c>
+      <c r="D84" t="s">
+        <v>103</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>37</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="I84">
+        <v>1.41</v>
+      </c>
+      <c r="J84">
+        <v>0.59</v>
+      </c>
+      <c r="K84">
+        <v>16</v>
+      </c>
+      <c r="L84">
+        <v>9</v>
+      </c>
+      <c r="M84">
+        <v>3</v>
+      </c>
+      <c r="N84">
+        <v>2</v>
+      </c>
+      <c r="O84">
+        <v>5</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>5</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>267</v>
+      </c>
+      <c r="T84">
+        <v>483</v>
+      </c>
+      <c r="U84">
+        <v>14</v>
+      </c>
+      <c r="V84">
+        <v>13</v>
+      </c>
+      <c r="W84">
+        <v>2</v>
+      </c>
+      <c r="X84">
+        <v>6</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA84">
+        <v>12</v>
+      </c>
+      <c r="AB84">
+        <v>7</v>
+      </c>
+      <c r="AC84">
+        <v>1</v>
+      </c>
+      <c r="AD84">
+        <v>0</v>
+      </c>
+      <c r="AE84">
+        <v>0</v>
+      </c>
+      <c r="AF84">
+        <v>0</v>
+      </c>
+      <c r="AG84">
+        <v>13</v>
+      </c>
+      <c r="AH84">
+        <v>7</v>
+      </c>
+      <c r="AI84">
+        <v>3</v>
+      </c>
+      <c r="AJ84">
+        <v>2</v>
+      </c>
+      <c r="AK84">
+        <v>1.29</v>
+      </c>
+      <c r="AL84">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AM84">
+        <v>0.12</v>
+      </c>
+      <c r="AN84">
+        <v>0.04</v>
+      </c>
+      <c r="AO84">
+        <v>1.41</v>
+      </c>
+      <c r="AP84">
+        <v>0.59</v>
+      </c>
+      <c r="AQ84">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AR84">
+        <v>0.1</v>
+      </c>
+      <c r="AS84">
+        <v>334</v>
+      </c>
+      <c r="AT84">
+        <v>568</v>
+      </c>
+      <c r="AU84">
+        <v>158</v>
+      </c>
+      <c r="AV84">
+        <v>186</v>
+      </c>
+      <c r="AW84">
+        <v>109</v>
+      </c>
+      <c r="AX84">
+        <v>297</v>
+      </c>
+      <c r="AY84">
+        <v>28</v>
+      </c>
+      <c r="AZ84">
+        <v>29</v>
+      </c>
+      <c r="BA84">
+        <v>4</v>
+      </c>
+      <c r="BB84">
+        <v>3</v>
+      </c>
+      <c r="BC84">
+        <v>15</v>
+      </c>
+      <c r="BD84">
+        <v>13</v>
+      </c>
+      <c r="BE84">
+        <v>19</v>
+      </c>
+      <c r="BF84">
+        <v>30</v>
+      </c>
+      <c r="BG84">
+        <v>2</v>
+      </c>
+      <c r="BH84">
+        <v>1</v>
+      </c>
+      <c r="BI84" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ84" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK84">
+        <v>17</v>
+      </c>
+      <c r="BL84">
+        <v>14</v>
+      </c>
+      <c r="BM84">
+        <v>16</v>
+      </c>
+      <c r="BN84">
+        <v>7</v>
+      </c>
+      <c r="BO84">
+        <v>1</v>
+      </c>
+      <c r="BP84">
+        <v>1</v>
+      </c>
+      <c r="BQ84">
+        <v>35</v>
+      </c>
+      <c r="BR84">
+        <v>18</v>
+      </c>
+      <c r="BS84">
+        <v>1</v>
+      </c>
+      <c r="BT84">
+        <v>3</v>
+      </c>
+      <c r="BU84" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV84" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW84">
+        <v>51</v>
+      </c>
+      <c r="BX84">
+        <v>45</v>
+      </c>
+      <c r="BY84">
+        <v>36</v>
+      </c>
+      <c r="BZ84">
+        <v>32</v>
+      </c>
+      <c r="CA84">
+        <v>15</v>
+      </c>
+      <c r="CB84">
+        <v>13</v>
+      </c>
+      <c r="CC84">
+        <v>7</v>
+      </c>
+      <c r="CD84">
+        <v>4</v>
+      </c>
+      <c r="CE84" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF84" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG84">
+        <v>3</v>
+      </c>
+      <c r="CH84">
+        <v>3</v>
+      </c>
+      <c r="CI84">
+        <v>0</v>
+      </c>
+      <c r="CJ84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:88" ht="30">
+      <c r="B85" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C85" t="s">
+        <v>121</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>44</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="I85">
+        <v>3.38</v>
+      </c>
+      <c r="J85">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K85">
+        <v>20</v>
+      </c>
+      <c r="L85">
+        <v>9</v>
+      </c>
+      <c r="M85">
+        <v>7</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85">
+        <v>3</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>1</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <v>244</v>
+      </c>
+      <c r="T85">
+        <v>362</v>
+      </c>
+      <c r="U85">
+        <v>21</v>
+      </c>
+      <c r="V85">
+        <v>9</v>
+      </c>
+      <c r="W85">
+        <v>7</v>
+      </c>
+      <c r="X85">
+        <v>4</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA85">
+        <v>9</v>
+      </c>
+      <c r="AB85">
+        <v>5</v>
+      </c>
+      <c r="AC85">
+        <v>4</v>
+      </c>
+      <c r="AD85">
+        <v>3</v>
+      </c>
+      <c r="AE85">
+        <v>0</v>
+      </c>
+      <c r="AF85">
+        <v>0</v>
+      </c>
+      <c r="AG85">
+        <v>16</v>
+      </c>
+      <c r="AH85">
+        <v>1</v>
+      </c>
+      <c r="AI85">
+        <v>4</v>
+      </c>
+      <c r="AJ85">
+        <v>8</v>
+      </c>
+      <c r="AK85">
+        <v>0.72</v>
+      </c>
+      <c r="AL85">
+        <v>0.24</v>
+      </c>
+      <c r="AM85">
+        <v>1.88</v>
+      </c>
+      <c r="AN85">
+        <v>0.05</v>
+      </c>
+      <c r="AO85">
+        <v>2.59</v>
+      </c>
+      <c r="AP85">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AQ85">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="AR85">
+        <v>0.01</v>
+      </c>
+      <c r="AS85">
+        <v>327</v>
+      </c>
+      <c r="AT85">
+        <v>424</v>
+      </c>
+      <c r="AU85">
+        <v>148</v>
+      </c>
+      <c r="AV85">
+        <v>184</v>
+      </c>
+      <c r="AW85">
+        <v>96</v>
+      </c>
+      <c r="AX85">
+        <v>178</v>
+      </c>
+      <c r="AY85">
+        <v>34</v>
+      </c>
+      <c r="AZ85">
+        <v>5</v>
+      </c>
+      <c r="BA85">
+        <v>7</v>
+      </c>
+      <c r="BB85">
+        <v>2</v>
+      </c>
+      <c r="BC85">
+        <v>24</v>
+      </c>
+      <c r="BD85">
+        <v>26</v>
+      </c>
+      <c r="BE85">
+        <v>30</v>
+      </c>
+      <c r="BF85">
+        <v>5</v>
+      </c>
+      <c r="BG85">
+        <v>4</v>
+      </c>
+      <c r="BH85">
+        <v>2</v>
+      </c>
+      <c r="BI85" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ85" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK85">
+        <v>15</v>
+      </c>
+      <c r="BL85">
+        <v>14</v>
+      </c>
+      <c r="BM85">
+        <v>5</v>
+      </c>
+      <c r="BN85">
+        <v>8</v>
+      </c>
+      <c r="BO85">
+        <v>2</v>
+      </c>
+      <c r="BP85">
+        <v>3</v>
+      </c>
+      <c r="BQ85">
+        <v>22</v>
+      </c>
+      <c r="BR85">
+        <v>32</v>
+      </c>
+      <c r="BS85">
+        <v>1</v>
+      </c>
+      <c r="BT85">
+        <v>5</v>
+      </c>
+      <c r="BU85" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV85" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW85">
+        <v>41</v>
+      </c>
+      <c r="BX85">
+        <v>50</v>
+      </c>
+      <c r="BY85">
+        <v>28</v>
+      </c>
+      <c r="BZ85">
+        <v>40</v>
+      </c>
+      <c r="CA85">
+        <v>13</v>
+      </c>
+      <c r="CB85">
+        <v>10</v>
+      </c>
+      <c r="CC85">
+        <v>6</v>
+      </c>
+      <c r="CD85">
+        <v>8</v>
+      </c>
+      <c r="CE85" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF85" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG85">
+        <v>2</v>
+      </c>
+      <c r="CH85">
+        <v>3</v>
+      </c>
+      <c r="CI85">
+        <v>0</v>
+      </c>
+      <c r="CJ85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:88" ht="30">
+      <c r="B86" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86">
+        <v>48</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="I86">
+        <v>0.87</v>
+      </c>
+      <c r="J86">
+        <v>1.03</v>
+      </c>
+      <c r="K86">
+        <v>6</v>
+      </c>
+      <c r="L86">
+        <v>20</v>
+      </c>
+      <c r="M86">
+        <v>3</v>
+      </c>
+      <c r="N86">
+        <v>9</v>
+      </c>
+      <c r="O86">
+        <v>1</v>
+      </c>
+      <c r="P86">
+        <v>1</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <v>1</v>
+      </c>
+      <c r="S86">
+        <v>383</v>
+      </c>
+      <c r="T86">
+        <v>396</v>
+      </c>
+      <c r="U86">
+        <v>14</v>
+      </c>
+      <c r="V86">
+        <v>17</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
+      <c r="X86">
+        <v>4</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA86">
+        <v>3</v>
+      </c>
+      <c r="AB86">
+        <v>5</v>
+      </c>
+      <c r="AC86">
+        <v>0</v>
+      </c>
+      <c r="AD86">
+        <v>6</v>
+      </c>
+      <c r="AE86">
+        <v>0</v>
+      </c>
+      <c r="AF86">
+        <v>0</v>
+      </c>
+      <c r="AG86">
+        <v>3</v>
+      </c>
+      <c r="AH86">
+        <v>14</v>
+      </c>
+      <c r="AI86">
+        <v>3</v>
+      </c>
+      <c r="AJ86">
+        <v>6</v>
+      </c>
+      <c r="AK86">
+        <v>0.73</v>
+      </c>
+      <c r="AL86">
+        <v>0.87</v>
+      </c>
+      <c r="AM86">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AN86">
+        <v>0.16</v>
+      </c>
+      <c r="AO86">
+        <v>0.87</v>
+      </c>
+      <c r="AP86">
+        <v>1.03</v>
+      </c>
+      <c r="AQ86">
+        <v>1.31</v>
+      </c>
+      <c r="AR86">
+        <v>2.15</v>
+      </c>
+      <c r="AS86">
+        <v>467</v>
+      </c>
+      <c r="AT86">
+        <v>489</v>
+      </c>
+      <c r="AU86">
+        <v>240</v>
+      </c>
+      <c r="AV86">
+        <v>159</v>
+      </c>
+      <c r="AW86">
+        <v>143</v>
+      </c>
+      <c r="AX86">
+        <v>237</v>
+      </c>
+      <c r="AY86">
+        <v>24</v>
+      </c>
+      <c r="AZ86">
+        <v>28</v>
+      </c>
+      <c r="BA86">
+        <v>1</v>
+      </c>
+      <c r="BB86">
+        <v>10</v>
+      </c>
+      <c r="BC86">
+        <v>10</v>
+      </c>
+      <c r="BD86">
+        <v>22</v>
+      </c>
+      <c r="BE86">
+        <v>12</v>
+      </c>
+      <c r="BF86">
+        <v>33</v>
+      </c>
+      <c r="BG86">
+        <v>0</v>
+      </c>
+      <c r="BH86">
+        <v>3</v>
+      </c>
+      <c r="BI86" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ86" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK86">
+        <v>15</v>
+      </c>
+      <c r="BL86">
+        <v>14</v>
+      </c>
+      <c r="BM86">
+        <v>8</v>
+      </c>
+      <c r="BN86">
+        <v>11</v>
+      </c>
+      <c r="BO86">
+        <v>6</v>
+      </c>
+      <c r="BP86">
+        <v>0</v>
+      </c>
+      <c r="BQ86">
+        <v>42</v>
+      </c>
+      <c r="BR86">
+        <v>14</v>
+      </c>
+      <c r="BS86">
+        <v>8</v>
+      </c>
+      <c r="BT86">
+        <v>1</v>
+      </c>
+      <c r="BU86" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV86" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW86">
+        <v>49</v>
+      </c>
+      <c r="BX86">
+        <v>52</v>
+      </c>
+      <c r="BY86">
+        <v>37</v>
+      </c>
+      <c r="BZ86">
+        <v>32</v>
+      </c>
+      <c r="CA86">
+        <v>12</v>
+      </c>
+      <c r="CB86">
+        <v>20</v>
+      </c>
+      <c r="CC86">
+        <v>5</v>
+      </c>
+      <c r="CD86">
+        <v>5</v>
+      </c>
+      <c r="CE86" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF86" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG86">
+        <v>1</v>
+      </c>
+      <c r="CH86">
+        <v>1</v>
+      </c>
+      <c r="CI86">
+        <v>0</v>
+      </c>
+      <c r="CJ86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:88" ht="25.5">
+      <c r="B87" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="F87">
+        <v>5</v>
+      </c>
+      <c r="G87">
+        <v>45</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="I87">
+        <v>1.06</v>
+      </c>
+      <c r="J87">
+        <v>2.41</v>
+      </c>
+      <c r="K87">
+        <v>17</v>
+      </c>
+      <c r="L87">
+        <v>21</v>
+      </c>
+      <c r="M87">
+        <v>6</v>
+      </c>
+      <c r="N87">
+        <v>9</v>
+      </c>
+      <c r="O87">
+        <v>4</v>
+      </c>
+      <c r="P87">
+        <v>4</v>
+      </c>
+      <c r="Q87">
+        <v>3</v>
+      </c>
+      <c r="R87">
+        <v>2</v>
+      </c>
+      <c r="S87">
+        <v>412</v>
+      </c>
+      <c r="T87">
+        <v>525</v>
+      </c>
+      <c r="U87">
+        <v>4</v>
+      </c>
+      <c r="V87">
+        <v>9</v>
+      </c>
+      <c r="W87">
+        <v>4</v>
+      </c>
+      <c r="X87">
+        <v>5</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA87">
+        <v>7</v>
+      </c>
+      <c r="AB87">
+        <v>6</v>
+      </c>
+      <c r="AC87">
+        <v>4</v>
+      </c>
+      <c r="AD87">
+        <v>6</v>
+      </c>
+      <c r="AE87">
+        <v>0</v>
+      </c>
+      <c r="AF87">
+        <v>1</v>
+      </c>
+      <c r="AG87">
+        <v>12</v>
+      </c>
+      <c r="AH87">
+        <v>12</v>
+      </c>
+      <c r="AI87">
+        <v>5</v>
+      </c>
+      <c r="AJ87">
+        <v>9</v>
+      </c>
+      <c r="AK87">
+        <v>0.88</v>
+      </c>
+      <c r="AL87">
+        <v>2.21</v>
+      </c>
+      <c r="AM87">
+        <v>0.18</v>
+      </c>
+      <c r="AN87">
+        <v>0.19</v>
+      </c>
+      <c r="AO87">
+        <v>1.06</v>
+      </c>
+      <c r="AP87">
+        <v>2.41</v>
+      </c>
+      <c r="AQ87">
+        <v>2.16</v>
+      </c>
+      <c r="AR87">
+        <v>2.86</v>
+      </c>
+      <c r="AS87">
+        <v>477</v>
+      </c>
+      <c r="AT87">
+        <v>589</v>
+      </c>
+      <c r="AU87">
+        <v>242</v>
+      </c>
+      <c r="AV87">
+        <v>314</v>
+      </c>
+      <c r="AW87">
+        <v>169</v>
+      </c>
+      <c r="AX87">
+        <v>211</v>
+      </c>
+      <c r="AY87">
+        <v>17</v>
+      </c>
+      <c r="AZ87">
+        <v>23</v>
+      </c>
+      <c r="BA87">
+        <v>5</v>
+      </c>
+      <c r="BB87">
+        <v>4</v>
+      </c>
+      <c r="BC87">
+        <v>19</v>
+      </c>
+      <c r="BD87">
+        <v>22</v>
+      </c>
+      <c r="BE87">
+        <v>31</v>
+      </c>
+      <c r="BF87">
+        <v>24</v>
+      </c>
+      <c r="BG87">
+        <v>2</v>
+      </c>
+      <c r="BH87">
+        <v>2</v>
+      </c>
+      <c r="BI87" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ87" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK87">
+        <v>22</v>
+      </c>
+      <c r="BL87">
+        <v>18</v>
+      </c>
+      <c r="BM87">
+        <v>7</v>
+      </c>
+      <c r="BN87">
+        <v>13</v>
+      </c>
+      <c r="BO87">
+        <v>6</v>
+      </c>
+      <c r="BP87">
+        <v>4</v>
+      </c>
+      <c r="BQ87">
+        <v>16</v>
+      </c>
+      <c r="BR87">
+        <v>21</v>
+      </c>
+      <c r="BS87">
+        <v>4</v>
+      </c>
+      <c r="BT87">
+        <v>4</v>
+      </c>
+      <c r="BU87" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV87" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW87">
+        <v>48</v>
+      </c>
+      <c r="BX87">
+        <v>30</v>
+      </c>
+      <c r="BY87">
+        <v>40</v>
+      </c>
+      <c r="BZ87">
+        <v>24</v>
+      </c>
+      <c r="CA87">
+        <v>8</v>
+      </c>
+      <c r="CB87">
+        <v>6</v>
+      </c>
+      <c r="CC87">
+        <v>10</v>
+      </c>
+      <c r="CD87">
+        <v>2</v>
+      </c>
+      <c r="CE87" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF87" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG87">
+        <v>0</v>
+      </c>
+      <c r="CH87">
+        <v>2</v>
+      </c>
+      <c r="CI87">
+        <v>0</v>
+      </c>
+      <c r="CJ87">
         <v>0</v>
       </c>
     </row>

--- a/La Liga 26-27.xlsx
+++ b/La Liga 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8A07AFD-203A-4FAB-B9F2-B5DCF16B621A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E44B3B5-F5C2-4A8C-A407-99AF18B1251E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="404" xr2:uid="{2BF33204-32E8-4B40-BC26-7C459B7DAA69}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="193">
   <si>
     <t>date</t>
   </si>
@@ -613,6 +613,12 @@
   <si>
     <t>Sun 18 October, 18:30</t>
   </si>
+  <si>
+    <t>Mon 19 October, 21:00</t>
+  </si>
+  <si>
+    <t>Fri 23 October, 21:00</t>
+  </si>
 </sst>
 </file>
 
@@ -1037,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886C5DDF-1A39-4E94-A421-1D1D9FD99BEC}">
-  <dimension ref="A1:CK87"/>
+  <dimension ref="A1:CK89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1367,7 +1373,7 @@
         <v>52</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H87" si="0">100-G2</f>
+        <f t="shared" ref="H2:H89" si="0">100-G2</f>
         <v>48</v>
       </c>
       <c r="I2">
@@ -24117,6 +24123,534 @@
         <v>0</v>
       </c>
       <c r="CJ87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:88" ht="30">
+      <c r="B88" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C88" t="s">
+        <v>88</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>31</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="I88">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J88">
+        <v>2.25</v>
+      </c>
+      <c r="K88">
+        <v>12</v>
+      </c>
+      <c r="L88">
+        <v>21</v>
+      </c>
+      <c r="M88">
+        <v>4</v>
+      </c>
+      <c r="N88">
+        <v>5</v>
+      </c>
+      <c r="O88">
+        <v>1</v>
+      </c>
+      <c r="P88">
+        <v>3</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>2</v>
+      </c>
+      <c r="S88">
+        <v>181</v>
+      </c>
+      <c r="T88">
+        <v>521</v>
+      </c>
+      <c r="U88">
+        <v>12</v>
+      </c>
+      <c r="V88">
+        <v>9</v>
+      </c>
+      <c r="W88">
+        <v>8</v>
+      </c>
+      <c r="X88">
+        <v>8</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA88">
+        <v>4</v>
+      </c>
+      <c r="AB88">
+        <v>8</v>
+      </c>
+      <c r="AC88">
+        <v>4</v>
+      </c>
+      <c r="AD88">
+        <v>8</v>
+      </c>
+      <c r="AE88">
+        <v>1</v>
+      </c>
+      <c r="AF88">
+        <v>0</v>
+      </c>
+      <c r="AG88">
+        <v>4</v>
+      </c>
+      <c r="AH88">
+        <v>8</v>
+      </c>
+      <c r="AI88">
+        <v>8</v>
+      </c>
+      <c r="AJ88">
+        <v>13</v>
+      </c>
+      <c r="AK88">
+        <v>0.41</v>
+      </c>
+      <c r="AL88">
+        <v>2.13</v>
+      </c>
+      <c r="AM88">
+        <v>0.16</v>
+      </c>
+      <c r="AN88">
+        <v>0.12</v>
+      </c>
+      <c r="AO88">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AP88">
+        <v>2.25</v>
+      </c>
+      <c r="AQ88">
+        <v>1.31</v>
+      </c>
+      <c r="AR88">
+        <v>1.47</v>
+      </c>
+      <c r="AS88">
+        <v>254</v>
+      </c>
+      <c r="AT88">
+        <v>581</v>
+      </c>
+      <c r="AU88">
+        <v>73</v>
+      </c>
+      <c r="AV88">
+        <v>269</v>
+      </c>
+      <c r="AW88">
+        <v>108</v>
+      </c>
+      <c r="AX88">
+        <v>252</v>
+      </c>
+      <c r="AY88">
+        <v>22</v>
+      </c>
+      <c r="AZ88">
+        <v>19</v>
+      </c>
+      <c r="BA88">
+        <v>5</v>
+      </c>
+      <c r="BB88">
+        <v>4</v>
+      </c>
+      <c r="BC88">
+        <v>13</v>
+      </c>
+      <c r="BD88">
+        <v>15</v>
+      </c>
+      <c r="BE88">
+        <v>10</v>
+      </c>
+      <c r="BF88">
+        <v>18</v>
+      </c>
+      <c r="BG88">
+        <v>0</v>
+      </c>
+      <c r="BH88">
+        <v>3</v>
+      </c>
+      <c r="BI88" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ88" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK88">
+        <v>13</v>
+      </c>
+      <c r="BL88">
+        <v>10</v>
+      </c>
+      <c r="BM88">
+        <v>9</v>
+      </c>
+      <c r="BN88">
+        <v>7</v>
+      </c>
+      <c r="BO88">
+        <v>8</v>
+      </c>
+      <c r="BP88">
+        <v>4</v>
+      </c>
+      <c r="BQ88">
+        <v>27</v>
+      </c>
+      <c r="BR88">
+        <v>27</v>
+      </c>
+      <c r="BS88">
+        <v>4</v>
+      </c>
+      <c r="BT88">
+        <v>3</v>
+      </c>
+      <c r="BU88" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV88" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW88">
+        <v>37</v>
+      </c>
+      <c r="BX88">
+        <v>36</v>
+      </c>
+      <c r="BY88">
+        <v>26</v>
+      </c>
+      <c r="BZ88">
+        <v>23</v>
+      </c>
+      <c r="CA88">
+        <v>11</v>
+      </c>
+      <c r="CB88">
+        <v>13</v>
+      </c>
+      <c r="CC88">
+        <v>5</v>
+      </c>
+      <c r="CD88">
+        <v>2</v>
+      </c>
+      <c r="CE88" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF88" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG88">
+        <v>6</v>
+      </c>
+      <c r="CH88">
+        <v>3</v>
+      </c>
+      <c r="CI88">
+        <v>1</v>
+      </c>
+      <c r="CJ88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:88" ht="30">
+      <c r="B89" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>50</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="I89">
+        <v>1.51</v>
+      </c>
+      <c r="J89">
+        <v>0.47</v>
+      </c>
+      <c r="K89">
+        <v>18</v>
+      </c>
+      <c r="L89">
+        <v>7</v>
+      </c>
+      <c r="M89">
+        <v>4</v>
+      </c>
+      <c r="N89">
+        <v>3</v>
+      </c>
+      <c r="O89">
+        <v>1</v>
+      </c>
+      <c r="P89">
+        <v>1</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>367</v>
+      </c>
+      <c r="T89">
+        <v>385</v>
+      </c>
+      <c r="U89">
+        <v>14</v>
+      </c>
+      <c r="V89">
+        <v>12</v>
+      </c>
+      <c r="W89">
+        <v>7</v>
+      </c>
+      <c r="X89">
+        <v>2</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA89">
+        <v>8</v>
+      </c>
+      <c r="AB89">
+        <v>4</v>
+      </c>
+      <c r="AC89">
+        <v>6</v>
+      </c>
+      <c r="AD89">
+        <v>0</v>
+      </c>
+      <c r="AE89">
+        <v>2</v>
+      </c>
+      <c r="AF89">
+        <v>0</v>
+      </c>
+      <c r="AG89">
+        <v>12</v>
+      </c>
+      <c r="AH89">
+        <v>5</v>
+      </c>
+      <c r="AI89">
+        <v>6</v>
+      </c>
+      <c r="AJ89">
+        <v>2</v>
+      </c>
+      <c r="AK89">
+        <v>0.81</v>
+      </c>
+      <c r="AL89">
+        <v>0.47</v>
+      </c>
+      <c r="AM89">
+        <v>0.71</v>
+      </c>
+      <c r="AN89">
+        <v>0</v>
+      </c>
+      <c r="AO89">
+        <v>1.51</v>
+      </c>
+      <c r="AP89">
+        <v>0.47</v>
+      </c>
+      <c r="AQ89">
+        <v>1.27</v>
+      </c>
+      <c r="AR89">
+        <v>0.67</v>
+      </c>
+      <c r="AS89">
+        <v>424</v>
+      </c>
+      <c r="AT89">
+        <v>465</v>
+      </c>
+      <c r="AU89">
+        <v>187</v>
+      </c>
+      <c r="AV89">
+        <v>221</v>
+      </c>
+      <c r="AW89">
+        <v>180</v>
+      </c>
+      <c r="AX89">
+        <v>164</v>
+      </c>
+      <c r="AY89">
+        <v>29</v>
+      </c>
+      <c r="AZ89">
+        <v>23</v>
+      </c>
+      <c r="BA89">
+        <v>10</v>
+      </c>
+      <c r="BB89">
+        <v>1</v>
+      </c>
+      <c r="BC89">
+        <v>32</v>
+      </c>
+      <c r="BD89">
+        <v>22</v>
+      </c>
+      <c r="BE89">
+        <v>29</v>
+      </c>
+      <c r="BF89">
+        <v>11</v>
+      </c>
+      <c r="BG89">
+        <v>0</v>
+      </c>
+      <c r="BH89">
+        <v>2</v>
+      </c>
+      <c r="BI89" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ89" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK89">
+        <v>24</v>
+      </c>
+      <c r="BL89">
+        <v>27</v>
+      </c>
+      <c r="BM89">
+        <v>8</v>
+      </c>
+      <c r="BN89">
+        <v>7</v>
+      </c>
+      <c r="BO89">
+        <v>0</v>
+      </c>
+      <c r="BP89">
+        <v>6</v>
+      </c>
+      <c r="BQ89">
+        <v>16</v>
+      </c>
+      <c r="BR89">
+        <v>37</v>
+      </c>
+      <c r="BS89">
+        <v>2</v>
+      </c>
+      <c r="BT89">
+        <v>3</v>
+      </c>
+      <c r="BU89" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV89" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW89">
+        <v>51</v>
+      </c>
+      <c r="BX89">
+        <v>63</v>
+      </c>
+      <c r="BY89">
+        <v>40</v>
+      </c>
+      <c r="BZ89">
+        <v>47</v>
+      </c>
+      <c r="CA89">
+        <v>11</v>
+      </c>
+      <c r="CB89">
+        <v>16</v>
+      </c>
+      <c r="CC89">
+        <v>5</v>
+      </c>
+      <c r="CD89">
+        <v>6</v>
+      </c>
+      <c r="CE89" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF89" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG89">
+        <v>2</v>
+      </c>
+      <c r="CH89">
+        <v>1</v>
+      </c>
+      <c r="CI89">
+        <v>0</v>
+      </c>
+      <c r="CJ89">
         <v>0</v>
       </c>
     </row>

--- a/La Liga 26-27.xlsx
+++ b/La Liga 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E44B3B5-F5C2-4A8C-A407-99AF18B1251E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9843AC58-8270-499D-AC7E-26A490D60E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="404" xr2:uid="{2BF33204-32E8-4B40-BC26-7C459B7DAA69}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="194">
   <si>
     <t>date</t>
   </si>
@@ -619,6 +619,9 @@
   <si>
     <t>Fri 23 October, 21:00</t>
   </si>
+  <si>
+    <t>Sun 18 October, 21:00</t>
+  </si>
 </sst>
 </file>
 
@@ -1043,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886C5DDF-1A39-4E94-A421-1D1D9FD99BEC}">
-  <dimension ref="A1:CK89"/>
+  <dimension ref="A1:CK90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1373,7 +1376,7 @@
         <v>52</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H89" si="0">100-G2</f>
+        <f t="shared" ref="H2:H90" si="0">100-G2</f>
         <v>48</v>
       </c>
       <c r="I2">
@@ -24126,184 +24129,184 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:88" ht="30">
-      <c r="B88" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C88" t="s">
-        <v>88</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>91</v>
+    <row r="88" spans="2:88" ht="25.5">
+      <c r="B88" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D88" t="s">
+        <v>90</v>
       </c>
       <c r="E88">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="H88">
         <f t="shared" si="0"/>
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="I88">
-        <v>0.56999999999999995</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="J88">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="K88">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L88">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M88">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N88">
         <v>5</v>
       </c>
       <c r="O88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P88">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q88">
         <v>0</v>
       </c>
       <c r="R88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S88">
-        <v>181</v>
+        <v>605</v>
       </c>
       <c r="T88">
-        <v>521</v>
+        <v>280</v>
       </c>
       <c r="U88">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V88">
+        <v>14</v>
+      </c>
+      <c r="W88">
+        <v>1</v>
+      </c>
+      <c r="X88">
+        <v>2</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA88">
+        <v>5</v>
+      </c>
+      <c r="AB88">
+        <v>4</v>
+      </c>
+      <c r="AC88">
+        <v>2</v>
+      </c>
+      <c r="AD88">
+        <v>2</v>
+      </c>
+      <c r="AE88">
+        <v>0</v>
+      </c>
+      <c r="AF88">
+        <v>0</v>
+      </c>
+      <c r="AG88">
+        <v>10</v>
+      </c>
+      <c r="AH88">
         <v>9</v>
       </c>
-      <c r="W88">
-        <v>8</v>
-      </c>
-      <c r="X88">
-        <v>8</v>
-      </c>
-      <c r="Y88" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z88" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA88">
-        <v>4</v>
-      </c>
-      <c r="AB88">
-        <v>8</v>
-      </c>
-      <c r="AC88">
-        <v>4</v>
-      </c>
-      <c r="AD88">
-        <v>8</v>
-      </c>
-      <c r="AE88">
-        <v>1</v>
-      </c>
-      <c r="AF88">
-        <v>0</v>
-      </c>
-      <c r="AG88">
-        <v>4</v>
-      </c>
-      <c r="AH88">
-        <v>8</v>
-      </c>
       <c r="AI88">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AJ88">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AK88">
-        <v>0.41</v>
+        <v>1.46</v>
       </c>
       <c r="AL88">
-        <v>2.13</v>
+        <v>0.69</v>
       </c>
       <c r="AM88">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
       <c r="AN88">
-        <v>0.12</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AO88">
-        <v>0.56999999999999995</v>
+        <v>1.49</v>
       </c>
       <c r="AP88">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="AQ88">
-        <v>1.31</v>
+        <v>2.82</v>
       </c>
       <c r="AR88">
-        <v>1.47</v>
+        <v>1.07</v>
       </c>
       <c r="AS88">
-        <v>254</v>
+        <v>667</v>
       </c>
       <c r="AT88">
-        <v>581</v>
+        <v>349</v>
       </c>
       <c r="AU88">
-        <v>73</v>
+        <v>353</v>
       </c>
       <c r="AV88">
-        <v>269</v>
+        <v>129</v>
       </c>
       <c r="AW88">
-        <v>108</v>
+        <v>252</v>
       </c>
       <c r="AX88">
-        <v>252</v>
+        <v>151</v>
       </c>
       <c r="AY88">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="AZ88">
         <v>19</v>
       </c>
       <c r="BA88">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BB88">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC88">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BD88">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE88">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BF88">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BG88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH88">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI88" t="s">
         <v>89</v>
@@ -24312,64 +24315,64 @@
         <v>89</v>
       </c>
       <c r="BK88">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BL88">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BM88">
         <v>9</v>
       </c>
       <c r="BN88">
+        <v>9</v>
+      </c>
+      <c r="BO88">
+        <v>2</v>
+      </c>
+      <c r="BP88">
+        <v>2</v>
+      </c>
+      <c r="BQ88">
+        <v>17</v>
+      </c>
+      <c r="BR88">
+        <v>15</v>
+      </c>
+      <c r="BS88">
+        <v>4</v>
+      </c>
+      <c r="BT88">
+        <v>3</v>
+      </c>
+      <c r="BU88" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV88" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW88">
+        <v>49</v>
+      </c>
+      <c r="BX88">
+        <v>45</v>
+      </c>
+      <c r="BY88">
+        <v>42</v>
+      </c>
+      <c r="BZ88">
+        <v>39</v>
+      </c>
+      <c r="CA88">
         <v>7</v>
       </c>
-      <c r="BO88">
-        <v>8</v>
-      </c>
-      <c r="BP88">
-        <v>4</v>
-      </c>
-      <c r="BQ88">
-        <v>27</v>
-      </c>
-      <c r="BR88">
-        <v>27</v>
-      </c>
-      <c r="BS88">
-        <v>4</v>
-      </c>
-      <c r="BT88">
-        <v>3</v>
-      </c>
-      <c r="BU88" t="s">
-        <v>89</v>
-      </c>
-      <c r="BV88" t="s">
-        <v>89</v>
-      </c>
-      <c r="BW88">
-        <v>37</v>
-      </c>
-      <c r="BX88">
-        <v>36</v>
-      </c>
-      <c r="BY88">
-        <v>26</v>
-      </c>
-      <c r="BZ88">
-        <v>23</v>
-      </c>
-      <c r="CA88">
+      <c r="CB88">
+        <v>6</v>
+      </c>
+      <c r="CC88">
         <v>11</v>
       </c>
-      <c r="CB88">
-        <v>13</v>
-      </c>
-      <c r="CC88">
-        <v>5</v>
-      </c>
       <c r="CD88">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="CE88" t="s">
         <v>89</v>
@@ -24378,13 +24381,13 @@
         <v>89</v>
       </c>
       <c r="CG88">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CH88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CI88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CJ88">
         <v>0</v>
@@ -24392,13 +24395,13 @@
     </row>
     <row r="89" spans="2:88" ht="30">
       <c r="B89" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>87</v>
+        <v>191</v>
+      </c>
+      <c r="C89" t="s">
+        <v>88</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E89">
         <v>1</v>
@@ -24407,250 +24410,514 @@
         <v>1</v>
       </c>
       <c r="G89">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="H89">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I89">
-        <v>1.51</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="J89">
-        <v>0.47</v>
+        <v>2.25</v>
       </c>
       <c r="K89">
+        <v>12</v>
+      </c>
+      <c r="L89">
+        <v>21</v>
+      </c>
+      <c r="M89">
+        <v>4</v>
+      </c>
+      <c r="N89">
+        <v>5</v>
+      </c>
+      <c r="O89">
+        <v>1</v>
+      </c>
+      <c r="P89">
+        <v>3</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>2</v>
+      </c>
+      <c r="S89">
+        <v>181</v>
+      </c>
+      <c r="T89">
+        <v>521</v>
+      </c>
+      <c r="U89">
+        <v>12</v>
+      </c>
+      <c r="V89">
+        <v>9</v>
+      </c>
+      <c r="W89">
+        <v>8</v>
+      </c>
+      <c r="X89">
+        <v>8</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA89">
+        <v>4</v>
+      </c>
+      <c r="AB89">
+        <v>8</v>
+      </c>
+      <c r="AC89">
+        <v>4</v>
+      </c>
+      <c r="AD89">
+        <v>8</v>
+      </c>
+      <c r="AE89">
+        <v>1</v>
+      </c>
+      <c r="AF89">
+        <v>0</v>
+      </c>
+      <c r="AG89">
+        <v>4</v>
+      </c>
+      <c r="AH89">
+        <v>8</v>
+      </c>
+      <c r="AI89">
+        <v>8</v>
+      </c>
+      <c r="AJ89">
+        <v>13</v>
+      </c>
+      <c r="AK89">
+        <v>0.41</v>
+      </c>
+      <c r="AL89">
+        <v>2.13</v>
+      </c>
+      <c r="AM89">
+        <v>0.16</v>
+      </c>
+      <c r="AN89">
+        <v>0.12</v>
+      </c>
+      <c r="AO89">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AP89">
+        <v>2.25</v>
+      </c>
+      <c r="AQ89">
+        <v>1.31</v>
+      </c>
+      <c r="AR89">
+        <v>1.47</v>
+      </c>
+      <c r="AS89">
+        <v>254</v>
+      </c>
+      <c r="AT89">
+        <v>581</v>
+      </c>
+      <c r="AU89">
+        <v>73</v>
+      </c>
+      <c r="AV89">
+        <v>269</v>
+      </c>
+      <c r="AW89">
+        <v>108</v>
+      </c>
+      <c r="AX89">
+        <v>252</v>
+      </c>
+      <c r="AY89">
+        <v>22</v>
+      </c>
+      <c r="AZ89">
+        <v>19</v>
+      </c>
+      <c r="BA89">
+        <v>5</v>
+      </c>
+      <c r="BB89">
+        <v>4</v>
+      </c>
+      <c r="BC89">
+        <v>13</v>
+      </c>
+      <c r="BD89">
+        <v>15</v>
+      </c>
+      <c r="BE89">
+        <v>10</v>
+      </c>
+      <c r="BF89">
         <v>18</v>
       </c>
-      <c r="L89">
-        <v>7</v>
-      </c>
-      <c r="M89">
-        <v>4</v>
-      </c>
-      <c r="N89">
-        <v>3</v>
-      </c>
-      <c r="O89">
-        <v>1</v>
-      </c>
-      <c r="P89">
-        <v>1</v>
-      </c>
-      <c r="Q89">
-        <v>0</v>
-      </c>
-      <c r="R89">
-        <v>0</v>
-      </c>
-      <c r="S89">
-        <v>367</v>
-      </c>
-      <c r="T89">
-        <v>385</v>
-      </c>
-      <c r="U89">
-        <v>14</v>
-      </c>
-      <c r="V89">
-        <v>12</v>
-      </c>
-      <c r="W89">
-        <v>7</v>
-      </c>
-      <c r="X89">
-        <v>2</v>
-      </c>
-      <c r="Y89" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z89" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA89">
-        <v>8</v>
-      </c>
-      <c r="AB89">
-        <v>4</v>
-      </c>
-      <c r="AC89">
-        <v>6</v>
-      </c>
-      <c r="AD89">
-        <v>0</v>
-      </c>
-      <c r="AE89">
-        <v>2</v>
-      </c>
-      <c r="AF89">
-        <v>0</v>
-      </c>
-      <c r="AG89">
-        <v>12</v>
-      </c>
-      <c r="AH89">
-        <v>5</v>
-      </c>
-      <c r="AI89">
-        <v>6</v>
-      </c>
-      <c r="AJ89">
-        <v>2</v>
-      </c>
-      <c r="AK89">
-        <v>0.81</v>
-      </c>
-      <c r="AL89">
-        <v>0.47</v>
-      </c>
-      <c r="AM89">
-        <v>0.71</v>
-      </c>
-      <c r="AN89">
-        <v>0</v>
-      </c>
-      <c r="AO89">
-        <v>1.51</v>
-      </c>
-      <c r="AP89">
-        <v>0.47</v>
-      </c>
-      <c r="AQ89">
-        <v>1.27</v>
-      </c>
-      <c r="AR89">
-        <v>0.67</v>
-      </c>
-      <c r="AS89">
-        <v>424</v>
-      </c>
-      <c r="AT89">
-        <v>465</v>
-      </c>
-      <c r="AU89">
-        <v>187</v>
-      </c>
-      <c r="AV89">
-        <v>221</v>
-      </c>
-      <c r="AW89">
-        <v>180</v>
-      </c>
-      <c r="AX89">
-        <v>164</v>
-      </c>
-      <c r="AY89">
-        <v>29</v>
-      </c>
-      <c r="AZ89">
-        <v>23</v>
-      </c>
-      <c r="BA89">
+      <c r="BG89">
+        <v>0</v>
+      </c>
+      <c r="BH89">
+        <v>3</v>
+      </c>
+      <c r="BI89" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ89" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK89">
+        <v>13</v>
+      </c>
+      <c r="BL89">
         <v>10</v>
       </c>
-      <c r="BB89">
-        <v>1</v>
-      </c>
-      <c r="BC89">
-        <v>32</v>
-      </c>
-      <c r="BD89">
-        <v>22</v>
-      </c>
-      <c r="BE89">
-        <v>29</v>
-      </c>
-      <c r="BF89">
-        <v>11</v>
-      </c>
-      <c r="BG89">
-        <v>0</v>
-      </c>
-      <c r="BH89">
-        <v>2</v>
-      </c>
-      <c r="BI89" t="s">
-        <v>89</v>
-      </c>
-      <c r="BJ89" t="s">
-        <v>89</v>
-      </c>
-      <c r="BK89">
-        <v>24</v>
-      </c>
-      <c r="BL89">
-        <v>27</v>
-      </c>
       <c r="BM89">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BN89">
         <v>7</v>
       </c>
       <c r="BO89">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BP89">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BQ89">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BR89">
+        <v>27</v>
+      </c>
+      <c r="BS89">
+        <v>4</v>
+      </c>
+      <c r="BT89">
+        <v>3</v>
+      </c>
+      <c r="BU89" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV89" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW89">
         <v>37</v>
       </c>
-      <c r="BS89">
-        <v>2</v>
-      </c>
-      <c r="BT89">
-        <v>3</v>
-      </c>
-      <c r="BU89" t="s">
-        <v>89</v>
-      </c>
-      <c r="BV89" t="s">
-        <v>89</v>
-      </c>
-      <c r="BW89">
-        <v>51</v>
-      </c>
       <c r="BX89">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="BY89">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="BZ89">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="CA89">
         <v>11</v>
       </c>
       <c r="CB89">
+        <v>13</v>
+      </c>
+      <c r="CC89">
+        <v>5</v>
+      </c>
+      <c r="CD89">
+        <v>2</v>
+      </c>
+      <c r="CE89" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF89" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG89">
+        <v>6</v>
+      </c>
+      <c r="CH89">
+        <v>3</v>
+      </c>
+      <c r="CI89">
+        <v>1</v>
+      </c>
+      <c r="CJ89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:88" ht="30">
+      <c r="B90" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>50</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="I90">
+        <v>1.51</v>
+      </c>
+      <c r="J90">
+        <v>0.47</v>
+      </c>
+      <c r="K90">
+        <v>18</v>
+      </c>
+      <c r="L90">
+        <v>7</v>
+      </c>
+      <c r="M90">
+        <v>4</v>
+      </c>
+      <c r="N90">
+        <v>3</v>
+      </c>
+      <c r="O90">
+        <v>1</v>
+      </c>
+      <c r="P90">
+        <v>1</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>367</v>
+      </c>
+      <c r="T90">
+        <v>385</v>
+      </c>
+      <c r="U90">
+        <v>14</v>
+      </c>
+      <c r="V90">
+        <v>12</v>
+      </c>
+      <c r="W90">
+        <v>7</v>
+      </c>
+      <c r="X90">
+        <v>2</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA90">
+        <v>8</v>
+      </c>
+      <c r="AB90">
+        <v>4</v>
+      </c>
+      <c r="AC90">
+        <v>6</v>
+      </c>
+      <c r="AD90">
+        <v>0</v>
+      </c>
+      <c r="AE90">
+        <v>2</v>
+      </c>
+      <c r="AF90">
+        <v>0</v>
+      </c>
+      <c r="AG90">
+        <v>12</v>
+      </c>
+      <c r="AH90">
+        <v>5</v>
+      </c>
+      <c r="AI90">
+        <v>6</v>
+      </c>
+      <c r="AJ90">
+        <v>2</v>
+      </c>
+      <c r="AK90">
+        <v>0.81</v>
+      </c>
+      <c r="AL90">
+        <v>0.47</v>
+      </c>
+      <c r="AM90">
+        <v>0.71</v>
+      </c>
+      <c r="AN90">
+        <v>0</v>
+      </c>
+      <c r="AO90">
+        <v>1.51</v>
+      </c>
+      <c r="AP90">
+        <v>0.47</v>
+      </c>
+      <c r="AQ90">
+        <v>1.27</v>
+      </c>
+      <c r="AR90">
+        <v>0.67</v>
+      </c>
+      <c r="AS90">
+        <v>424</v>
+      </c>
+      <c r="AT90">
+        <v>465</v>
+      </c>
+      <c r="AU90">
+        <v>187</v>
+      </c>
+      <c r="AV90">
+        <v>221</v>
+      </c>
+      <c r="AW90">
+        <v>180</v>
+      </c>
+      <c r="AX90">
+        <v>164</v>
+      </c>
+      <c r="AY90">
+        <v>29</v>
+      </c>
+      <c r="AZ90">
+        <v>23</v>
+      </c>
+      <c r="BA90">
+        <v>10</v>
+      </c>
+      <c r="BB90">
+        <v>1</v>
+      </c>
+      <c r="BC90">
+        <v>32</v>
+      </c>
+      <c r="BD90">
+        <v>22</v>
+      </c>
+      <c r="BE90">
+        <v>29</v>
+      </c>
+      <c r="BF90">
+        <v>11</v>
+      </c>
+      <c r="BG90">
+        <v>0</v>
+      </c>
+      <c r="BH90">
+        <v>2</v>
+      </c>
+      <c r="BI90" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ90" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK90">
+        <v>24</v>
+      </c>
+      <c r="BL90">
+        <v>27</v>
+      </c>
+      <c r="BM90">
+        <v>8</v>
+      </c>
+      <c r="BN90">
+        <v>7</v>
+      </c>
+      <c r="BO90">
+        <v>0</v>
+      </c>
+      <c r="BP90">
+        <v>6</v>
+      </c>
+      <c r="BQ90">
         <v>16</v>
       </c>
-      <c r="CC89">
-        <v>5</v>
-      </c>
-      <c r="CD89">
+      <c r="BR90">
+        <v>37</v>
+      </c>
+      <c r="BS90">
+        <v>2</v>
+      </c>
+      <c r="BT90">
+        <v>3</v>
+      </c>
+      <c r="BU90" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV90" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW90">
+        <v>51</v>
+      </c>
+      <c r="BX90">
+        <v>63</v>
+      </c>
+      <c r="BY90">
+        <v>40</v>
+      </c>
+      <c r="BZ90">
+        <v>47</v>
+      </c>
+      <c r="CA90">
+        <v>11</v>
+      </c>
+      <c r="CB90">
+        <v>16</v>
+      </c>
+      <c r="CC90">
+        <v>5</v>
+      </c>
+      <c r="CD90">
         <v>6</v>
       </c>
-      <c r="CE89" t="s">
-        <v>89</v>
-      </c>
-      <c r="CF89" t="s">
-        <v>89</v>
-      </c>
-      <c r="CG89">
-        <v>2</v>
-      </c>
-      <c r="CH89">
-        <v>1</v>
-      </c>
-      <c r="CI89">
-        <v>0</v>
-      </c>
-      <c r="CJ89">
+      <c r="CE90" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF90" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG90">
+        <v>2</v>
+      </c>
+      <c r="CH90">
+        <v>1</v>
+      </c>
+      <c r="CI90">
+        <v>0</v>
+      </c>
+      <c r="CJ90">
         <v>0</v>
       </c>
     </row>

--- a/La Liga 26-27.xlsx
+++ b/La Liga 26-27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kuba\Desktop\analityczka\26-27\Ekstraklasa 26-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9843AC58-8270-499D-AC7E-26A490D60E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFCEC394-B76B-4EE1-B8DF-C46D10D9E7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="404" xr2:uid="{2BF33204-32E8-4B40-BC26-7C459B7DAA69}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="202">
   <si>
     <t>date</t>
   </si>
@@ -622,6 +622,30 @@
   <si>
     <t>Sun 18 October, 21:00</t>
   </si>
+  <si>
+    <t>Sat 24 October, 14:00</t>
+  </si>
+  <si>
+    <t>Sat 24 October, 16:15</t>
+  </si>
+  <si>
+    <t>Sat 24 October, 18:30</t>
+  </si>
+  <si>
+    <t>Sat 24 October, 21:00</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 14:00</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 16:15</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 18:30</t>
+  </si>
+  <si>
+    <t>Sun 25 October, 21:00</t>
+  </si>
 </sst>
 </file>
 
@@ -1046,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{886C5DDF-1A39-4E94-A421-1D1D9FD99BEC}">
-  <dimension ref="A1:CK90"/>
+  <dimension ref="A1:CK98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1376,7 +1400,7 @@
         <v>52</v>
       </c>
       <c r="H2">
-        <f t="shared" ref="H2:H90" si="0">100-G2</f>
+        <f t="shared" ref="H2:H98" si="0">100-G2</f>
         <v>48</v>
       </c>
       <c r="I2">
@@ -24918,6 +24942,2118 @@
         <v>0</v>
       </c>
       <c r="CJ90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:88" ht="25.5">
+      <c r="B91" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D91" t="s">
+        <v>98</v>
+      </c>
+      <c r="E91">
+        <v>3</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>57</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="I91">
+        <v>1.52</v>
+      </c>
+      <c r="J91">
+        <v>2.52</v>
+      </c>
+      <c r="K91">
+        <v>18</v>
+      </c>
+      <c r="L91">
+        <v>16</v>
+      </c>
+      <c r="M91">
+        <v>5</v>
+      </c>
+      <c r="N91">
+        <v>9</v>
+      </c>
+      <c r="O91">
+        <v>1</v>
+      </c>
+      <c r="P91">
+        <v>3</v>
+      </c>
+      <c r="Q91">
+        <v>1</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+      <c r="S91">
+        <v>436</v>
+      </c>
+      <c r="T91">
+        <v>319</v>
+      </c>
+      <c r="U91">
+        <v>15</v>
+      </c>
+      <c r="V91">
+        <v>11</v>
+      </c>
+      <c r="W91">
+        <v>3</v>
+      </c>
+      <c r="X91">
+        <v>3</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA91">
+        <v>10</v>
+      </c>
+      <c r="AB91">
+        <v>3</v>
+      </c>
+      <c r="AC91">
+        <v>3</v>
+      </c>
+      <c r="AD91">
+        <v>4</v>
+      </c>
+      <c r="AE91">
+        <v>1</v>
+      </c>
+      <c r="AF91">
+        <v>2</v>
+      </c>
+      <c r="AG91">
+        <v>8</v>
+      </c>
+      <c r="AH91">
+        <v>8</v>
+      </c>
+      <c r="AI91">
+        <v>10</v>
+      </c>
+      <c r="AJ91">
+        <v>8</v>
+      </c>
+      <c r="AK91">
+        <v>0.51</v>
+      </c>
+      <c r="AL91">
+        <v>0.66</v>
+      </c>
+      <c r="AM91">
+        <v>0.22</v>
+      </c>
+      <c r="AN91">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AO91">
+        <v>0.73</v>
+      </c>
+      <c r="AP91">
+        <v>0.94</v>
+      </c>
+      <c r="AQ91">
+        <v>0.67</v>
+      </c>
+      <c r="AR91">
+        <v>2.56</v>
+      </c>
+      <c r="AS91">
+        <v>494</v>
+      </c>
+      <c r="AT91">
+        <v>387</v>
+      </c>
+      <c r="AU91">
+        <v>192</v>
+      </c>
+      <c r="AV91">
+        <v>172</v>
+      </c>
+      <c r="AW91">
+        <v>244</v>
+      </c>
+      <c r="AX91">
+        <v>147</v>
+      </c>
+      <c r="AY91">
+        <v>25</v>
+      </c>
+      <c r="AZ91">
+        <v>34</v>
+      </c>
+      <c r="BA91">
+        <v>1</v>
+      </c>
+      <c r="BB91">
+        <v>3</v>
+      </c>
+      <c r="BC91">
+        <v>16</v>
+      </c>
+      <c r="BD91">
+        <v>13</v>
+      </c>
+      <c r="BE91">
+        <v>30</v>
+      </c>
+      <c r="BF91">
+        <v>23</v>
+      </c>
+      <c r="BG91">
+        <v>4</v>
+      </c>
+      <c r="BH91">
+        <v>2</v>
+      </c>
+      <c r="BI91" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ91" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK91">
+        <v>16</v>
+      </c>
+      <c r="BL91">
+        <v>15</v>
+      </c>
+      <c r="BM91">
+        <v>8</v>
+      </c>
+      <c r="BN91">
+        <v>13</v>
+      </c>
+      <c r="BO91">
+        <v>4</v>
+      </c>
+      <c r="BP91">
+        <v>4</v>
+      </c>
+      <c r="BQ91">
+        <v>14</v>
+      </c>
+      <c r="BR91">
+        <v>37</v>
+      </c>
+      <c r="BS91">
+        <v>6</v>
+      </c>
+      <c r="BT91">
+        <v>4</v>
+      </c>
+      <c r="BU91" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV91" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW91">
+        <v>43</v>
+      </c>
+      <c r="BX91">
+        <v>44</v>
+      </c>
+      <c r="BY91">
+        <v>35</v>
+      </c>
+      <c r="BZ91">
+        <v>37</v>
+      </c>
+      <c r="CA91">
+        <v>8</v>
+      </c>
+      <c r="CB91">
+        <v>7</v>
+      </c>
+      <c r="CC91">
+        <v>10</v>
+      </c>
+      <c r="CD91">
+        <v>7</v>
+      </c>
+      <c r="CE91" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF91" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG91">
+        <v>3</v>
+      </c>
+      <c r="CH91">
+        <v>3</v>
+      </c>
+      <c r="CI91">
+        <v>0</v>
+      </c>
+      <c r="CJ91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:88" ht="30">
+      <c r="B92" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D92" t="s">
+        <v>95</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>55</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="I92">
+        <v>2.27</v>
+      </c>
+      <c r="J92">
+        <v>0.52</v>
+      </c>
+      <c r="K92">
+        <v>23</v>
+      </c>
+      <c r="L92">
+        <v>11</v>
+      </c>
+      <c r="M92">
+        <v>9</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92">
+        <v>3</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>2</v>
+      </c>
+      <c r="R92">
+        <v>0</v>
+      </c>
+      <c r="S92">
+        <v>382</v>
+      </c>
+      <c r="T92">
+        <v>290</v>
+      </c>
+      <c r="U92">
+        <v>10</v>
+      </c>
+      <c r="V92">
+        <v>17</v>
+      </c>
+      <c r="W92">
+        <v>9</v>
+      </c>
+      <c r="X92">
+        <v>4</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA92">
+        <v>6</v>
+      </c>
+      <c r="AB92">
+        <v>4</v>
+      </c>
+      <c r="AC92">
+        <v>8</v>
+      </c>
+      <c r="AD92">
+        <v>6</v>
+      </c>
+      <c r="AE92">
+        <v>0</v>
+      </c>
+      <c r="AF92">
+        <v>0</v>
+      </c>
+      <c r="AG92">
+        <v>18</v>
+      </c>
+      <c r="AH92">
+        <v>9</v>
+      </c>
+      <c r="AI92">
+        <v>5</v>
+      </c>
+      <c r="AJ92">
+        <v>2</v>
+      </c>
+      <c r="AK92">
+        <v>1.02</v>
+      </c>
+      <c r="AL92">
+        <v>0.37</v>
+      </c>
+      <c r="AM92">
+        <v>1.25</v>
+      </c>
+      <c r="AN92">
+        <v>0.15</v>
+      </c>
+      <c r="AO92">
+        <v>2.27</v>
+      </c>
+      <c r="AP92">
+        <v>0.52</v>
+      </c>
+      <c r="AQ92">
+        <v>2.64</v>
+      </c>
+      <c r="AR92">
+        <v>0.48</v>
+      </c>
+      <c r="AS92">
+        <v>480</v>
+      </c>
+      <c r="AT92">
+        <v>380</v>
+      </c>
+      <c r="AU92">
+        <v>213</v>
+      </c>
+      <c r="AV92">
+        <v>170</v>
+      </c>
+      <c r="AW92">
+        <v>169</v>
+      </c>
+      <c r="AX92">
+        <v>120</v>
+      </c>
+      <c r="AY92">
+        <v>9</v>
+      </c>
+      <c r="AZ92">
+        <v>30</v>
+      </c>
+      <c r="BA92">
+        <v>6</v>
+      </c>
+      <c r="BB92">
+        <v>5</v>
+      </c>
+      <c r="BC92">
+        <v>15</v>
+      </c>
+      <c r="BD92">
+        <v>26</v>
+      </c>
+      <c r="BE92">
+        <v>43</v>
+      </c>
+      <c r="BF92">
+        <v>31</v>
+      </c>
+      <c r="BG92">
+        <v>1</v>
+      </c>
+      <c r="BH92">
+        <v>4</v>
+      </c>
+      <c r="BI92" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ92" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK92">
+        <v>16</v>
+      </c>
+      <c r="BL92">
+        <v>15</v>
+      </c>
+      <c r="BM92">
+        <v>11</v>
+      </c>
+      <c r="BN92">
+        <v>10</v>
+      </c>
+      <c r="BO92">
+        <v>6</v>
+      </c>
+      <c r="BP92">
+        <v>7</v>
+      </c>
+      <c r="BQ92">
+        <v>28</v>
+      </c>
+      <c r="BR92">
+        <v>39</v>
+      </c>
+      <c r="BS92">
+        <v>0</v>
+      </c>
+      <c r="BT92">
+        <v>7</v>
+      </c>
+      <c r="BU92" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV92" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW92">
+        <v>56</v>
+      </c>
+      <c r="BX92">
+        <v>46</v>
+      </c>
+      <c r="BY92">
+        <v>48</v>
+      </c>
+      <c r="BZ92">
+        <v>32</v>
+      </c>
+      <c r="CA92">
+        <v>8</v>
+      </c>
+      <c r="CB92">
+        <v>14</v>
+      </c>
+      <c r="CC92">
+        <v>15</v>
+      </c>
+      <c r="CD92">
+        <v>7</v>
+      </c>
+      <c r="CE92" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF92" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG92">
+        <v>3</v>
+      </c>
+      <c r="CH92">
+        <v>5</v>
+      </c>
+      <c r="CI92">
+        <v>0</v>
+      </c>
+      <c r="CJ92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:88" ht="25.5">
+      <c r="B93" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C93" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" t="s">
+        <v>93</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93">
+        <v>2</v>
+      </c>
+      <c r="G93">
+        <v>39</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="I93">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="J93">
+        <v>1.5</v>
+      </c>
+      <c r="K93">
+        <v>9</v>
+      </c>
+      <c r="L93">
+        <v>19</v>
+      </c>
+      <c r="M93">
+        <v>5</v>
+      </c>
+      <c r="N93">
+        <v>3</v>
+      </c>
+      <c r="O93">
+        <v>1</v>
+      </c>
+      <c r="P93">
+        <v>1</v>
+      </c>
+      <c r="Q93">
+        <v>0</v>
+      </c>
+      <c r="R93">
+        <v>0</v>
+      </c>
+      <c r="S93">
+        <v>249</v>
+      </c>
+      <c r="T93">
+        <v>465</v>
+      </c>
+      <c r="U93">
+        <v>18</v>
+      </c>
+      <c r="V93">
+        <v>9</v>
+      </c>
+      <c r="W93">
+        <v>6</v>
+      </c>
+      <c r="X93">
+        <v>9</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA93">
+        <v>3</v>
+      </c>
+      <c r="AB93">
+        <v>12</v>
+      </c>
+      <c r="AC93">
+        <v>1</v>
+      </c>
+      <c r="AD93">
+        <v>4</v>
+      </c>
+      <c r="AE93">
+        <v>0</v>
+      </c>
+      <c r="AF93">
+        <v>0</v>
+      </c>
+      <c r="AG93">
+        <v>7</v>
+      </c>
+      <c r="AH93">
+        <v>11</v>
+      </c>
+      <c r="AI93">
+        <v>2</v>
+      </c>
+      <c r="AJ93">
+        <v>8</v>
+      </c>
+      <c r="AK93">
+        <v>0.16</v>
+      </c>
+      <c r="AL93">
+        <v>1.28</v>
+      </c>
+      <c r="AM93">
+        <v>0.19</v>
+      </c>
+      <c r="AN93">
+        <v>0.21</v>
+      </c>
+      <c r="AO93">
+        <v>0.34</v>
+      </c>
+      <c r="AP93">
+        <v>1.5</v>
+      </c>
+      <c r="AQ93">
+        <v>1.28</v>
+      </c>
+      <c r="AR93">
+        <v>0.69</v>
+      </c>
+      <c r="AS93">
+        <v>333</v>
+      </c>
+      <c r="AT93">
+        <v>536</v>
+      </c>
+      <c r="AU93">
+        <v>127</v>
+      </c>
+      <c r="AV93">
+        <v>210</v>
+      </c>
+      <c r="AW93">
+        <v>122</v>
+      </c>
+      <c r="AX93">
+        <v>255</v>
+      </c>
+      <c r="AY93">
+        <v>17</v>
+      </c>
+      <c r="AZ93">
+        <v>27</v>
+      </c>
+      <c r="BA93">
+        <v>5</v>
+      </c>
+      <c r="BB93">
+        <v>4</v>
+      </c>
+      <c r="BC93">
+        <v>17</v>
+      </c>
+      <c r="BD93">
+        <v>16</v>
+      </c>
+      <c r="BE93">
+        <v>17</v>
+      </c>
+      <c r="BF93">
+        <v>43</v>
+      </c>
+      <c r="BG93">
+        <v>2</v>
+      </c>
+      <c r="BH93">
+        <v>2</v>
+      </c>
+      <c r="BI93" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ93" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK93">
+        <v>15</v>
+      </c>
+      <c r="BL93">
+        <v>16</v>
+      </c>
+      <c r="BM93">
+        <v>7</v>
+      </c>
+      <c r="BN93">
+        <v>13</v>
+      </c>
+      <c r="BO93">
+        <v>4</v>
+      </c>
+      <c r="BP93">
+        <v>1</v>
+      </c>
+      <c r="BQ93">
+        <v>29</v>
+      </c>
+      <c r="BR93">
+        <v>22</v>
+      </c>
+      <c r="BS93">
+        <v>1</v>
+      </c>
+      <c r="BT93">
+        <v>4</v>
+      </c>
+      <c r="BU93" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV93" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW93">
+        <v>43</v>
+      </c>
+      <c r="BX93">
+        <v>49</v>
+      </c>
+      <c r="BY93">
+        <v>30</v>
+      </c>
+      <c r="BZ93">
+        <v>41</v>
+      </c>
+      <c r="CA93">
+        <v>13</v>
+      </c>
+      <c r="CB93">
+        <v>8</v>
+      </c>
+      <c r="CC93">
+        <v>6</v>
+      </c>
+      <c r="CD93">
+        <v>9</v>
+      </c>
+      <c r="CE93" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF93" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG93">
+        <v>3</v>
+      </c>
+      <c r="CH93">
+        <v>3</v>
+      </c>
+      <c r="CI93">
+        <v>1</v>
+      </c>
+      <c r="CJ93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="2:88" ht="30">
+      <c r="B94" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>55</v>
+      </c>
+      <c r="H94">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="I94">
+        <v>1.41</v>
+      </c>
+      <c r="J94">
+        <v>1.67</v>
+      </c>
+      <c r="K94">
+        <v>20</v>
+      </c>
+      <c r="L94">
+        <v>15</v>
+      </c>
+      <c r="M94">
+        <v>4</v>
+      </c>
+      <c r="N94">
+        <v>5</v>
+      </c>
+      <c r="O94">
+        <v>3</v>
+      </c>
+      <c r="P94">
+        <v>3</v>
+      </c>
+      <c r="Q94">
+        <v>2</v>
+      </c>
+      <c r="R94">
+        <v>3</v>
+      </c>
+      <c r="S94">
+        <v>482</v>
+      </c>
+      <c r="T94">
+        <v>377</v>
+      </c>
+      <c r="U94">
+        <v>11</v>
+      </c>
+      <c r="V94">
+        <v>6</v>
+      </c>
+      <c r="W94">
+        <v>3</v>
+      </c>
+      <c r="X94">
+        <v>4</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA94">
+        <v>12</v>
+      </c>
+      <c r="AB94">
+        <v>7</v>
+      </c>
+      <c r="AC94">
+        <v>4</v>
+      </c>
+      <c r="AD94">
+        <v>3</v>
+      </c>
+      <c r="AE94">
+        <v>0</v>
+      </c>
+      <c r="AF94">
+        <v>0</v>
+      </c>
+      <c r="AG94">
+        <v>6</v>
+      </c>
+      <c r="AH94">
+        <v>10</v>
+      </c>
+      <c r="AI94">
+        <v>14</v>
+      </c>
+      <c r="AJ94">
+        <v>6</v>
+      </c>
+      <c r="AK94">
+        <v>1.28</v>
+      </c>
+      <c r="AL94">
+        <v>0.8</v>
+      </c>
+      <c r="AM94">
+        <v>0.13</v>
+      </c>
+      <c r="AN94">
+        <v>0.87</v>
+      </c>
+      <c r="AO94">
+        <v>1.41</v>
+      </c>
+      <c r="AP94">
+        <v>1.67</v>
+      </c>
+      <c r="AQ94">
+        <v>1.45</v>
+      </c>
+      <c r="AR94">
+        <v>0.99</v>
+      </c>
+      <c r="AS94">
+        <v>545</v>
+      </c>
+      <c r="AT94">
+        <v>434</v>
+      </c>
+      <c r="AU94">
+        <v>217</v>
+      </c>
+      <c r="AV94">
+        <v>171</v>
+      </c>
+      <c r="AW94">
+        <v>265</v>
+      </c>
+      <c r="AX94">
+        <v>206</v>
+      </c>
+      <c r="AY94">
+        <v>28</v>
+      </c>
+      <c r="AZ94">
+        <v>16</v>
+      </c>
+      <c r="BA94">
+        <v>1</v>
+      </c>
+      <c r="BB94">
+        <v>3</v>
+      </c>
+      <c r="BC94">
+        <v>18</v>
+      </c>
+      <c r="BD94">
+        <v>16</v>
+      </c>
+      <c r="BE94">
+        <v>21</v>
+      </c>
+      <c r="BF94">
+        <v>25</v>
+      </c>
+      <c r="BG94">
+        <v>1</v>
+      </c>
+      <c r="BH94">
+        <v>0</v>
+      </c>
+      <c r="BI94" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ94" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK94">
+        <v>16</v>
+      </c>
+      <c r="BL94">
+        <v>11</v>
+      </c>
+      <c r="BM94">
+        <v>5</v>
+      </c>
+      <c r="BN94">
+        <v>16</v>
+      </c>
+      <c r="BO94">
+        <v>2</v>
+      </c>
+      <c r="BP94">
+        <v>4</v>
+      </c>
+      <c r="BQ94">
+        <v>11</v>
+      </c>
+      <c r="BR94">
+        <v>19</v>
+      </c>
+      <c r="BS94">
+        <v>5</v>
+      </c>
+      <c r="BT94">
+        <v>3</v>
+      </c>
+      <c r="BU94" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV94" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW94">
+        <v>38</v>
+      </c>
+      <c r="BX94">
+        <v>41</v>
+      </c>
+      <c r="BY94">
+        <v>31</v>
+      </c>
+      <c r="BZ94">
+        <v>37</v>
+      </c>
+      <c r="CA94">
+        <v>7</v>
+      </c>
+      <c r="CB94">
+        <v>4</v>
+      </c>
+      <c r="CC94">
+        <v>9</v>
+      </c>
+      <c r="CD94">
+        <v>16</v>
+      </c>
+      <c r="CE94" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF94" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG94">
+        <v>4</v>
+      </c>
+      <c r="CH94">
+        <v>3</v>
+      </c>
+      <c r="CI94">
+        <v>0</v>
+      </c>
+      <c r="CJ94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:88" ht="25.5">
+      <c r="B95" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C95" t="s">
+        <v>103</v>
+      </c>
+      <c r="D95" t="s">
+        <v>88</v>
+      </c>
+      <c r="E95">
+        <v>4</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>62</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="I95">
+        <v>0.72</v>
+      </c>
+      <c r="J95">
+        <v>0.43</v>
+      </c>
+      <c r="K95">
+        <v>11</v>
+      </c>
+      <c r="L95">
+        <v>7</v>
+      </c>
+      <c r="M95">
+        <v>4</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95">
+        <v>1</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>0</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+      <c r="S95">
+        <v>518</v>
+      </c>
+      <c r="T95">
+        <v>274</v>
+      </c>
+      <c r="U95">
+        <v>11</v>
+      </c>
+      <c r="V95">
+        <v>15</v>
+      </c>
+      <c r="W95">
+        <v>2</v>
+      </c>
+      <c r="X95">
+        <v>4</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA95">
+        <v>4</v>
+      </c>
+      <c r="AB95">
+        <v>4</v>
+      </c>
+      <c r="AC95">
+        <v>3</v>
+      </c>
+      <c r="AD95">
+        <v>2</v>
+      </c>
+      <c r="AE95">
+        <v>0</v>
+      </c>
+      <c r="AF95">
+        <v>0</v>
+      </c>
+      <c r="AG95">
+        <v>6</v>
+      </c>
+      <c r="AH95">
+        <v>4</v>
+      </c>
+      <c r="AI95">
+        <v>5</v>
+      </c>
+      <c r="AJ95">
+        <v>3</v>
+      </c>
+      <c r="AK95">
+        <v>0.5</v>
+      </c>
+      <c r="AL95">
+        <v>0.33</v>
+      </c>
+      <c r="AM95">
+        <v>0.22</v>
+      </c>
+      <c r="AN95">
+        <v>0.1</v>
+      </c>
+      <c r="AO95">
+        <v>0.72</v>
+      </c>
+      <c r="AP95">
+        <v>0.43</v>
+      </c>
+      <c r="AQ95">
+        <v>0.72</v>
+      </c>
+      <c r="AR95">
+        <v>0.22</v>
+      </c>
+      <c r="AS95">
+        <v>589</v>
+      </c>
+      <c r="AT95">
+        <v>345</v>
+      </c>
+      <c r="AU95">
+        <v>265</v>
+      </c>
+      <c r="AV95">
+        <v>159</v>
+      </c>
+      <c r="AW95">
+        <v>253</v>
+      </c>
+      <c r="AX95">
+        <v>115</v>
+      </c>
+      <c r="AY95">
+        <v>38</v>
+      </c>
+      <c r="AZ95">
+        <v>29</v>
+      </c>
+      <c r="BA95">
+        <v>1</v>
+      </c>
+      <c r="BB95">
+        <v>3</v>
+      </c>
+      <c r="BC95">
+        <v>12</v>
+      </c>
+      <c r="BD95">
+        <v>15</v>
+      </c>
+      <c r="BE95">
+        <v>23</v>
+      </c>
+      <c r="BF95">
+        <v>11</v>
+      </c>
+      <c r="BG95">
+        <v>0</v>
+      </c>
+      <c r="BH95">
+        <v>2</v>
+      </c>
+      <c r="BI95" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ95" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK95">
+        <v>14</v>
+      </c>
+      <c r="BL95">
+        <v>13</v>
+      </c>
+      <c r="BM95">
+        <v>9</v>
+      </c>
+      <c r="BN95">
+        <v>8</v>
+      </c>
+      <c r="BO95">
+        <v>2</v>
+      </c>
+      <c r="BP95">
+        <v>3</v>
+      </c>
+      <c r="BQ95">
+        <v>16</v>
+      </c>
+      <c r="BR95">
+        <v>34</v>
+      </c>
+      <c r="BS95">
+        <v>1</v>
+      </c>
+      <c r="BT95">
+        <v>0</v>
+      </c>
+      <c r="BU95" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV95" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW95">
+        <v>45</v>
+      </c>
+      <c r="BX95">
+        <v>34</v>
+      </c>
+      <c r="BY95">
+        <v>34</v>
+      </c>
+      <c r="BZ95">
+        <v>28</v>
+      </c>
+      <c r="CA95">
+        <v>11</v>
+      </c>
+      <c r="CB95">
+        <v>6</v>
+      </c>
+      <c r="CC95">
+        <v>7</v>
+      </c>
+      <c r="CD95">
+        <v>5</v>
+      </c>
+      <c r="CE95" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF95" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG95">
+        <v>1</v>
+      </c>
+      <c r="CH95">
+        <v>3</v>
+      </c>
+      <c r="CI95">
+        <v>0</v>
+      </c>
+      <c r="CJ95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="2:88" ht="25.5">
+      <c r="B96" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D96" t="s">
+        <v>101</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>44</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="I96">
+        <v>0.76</v>
+      </c>
+      <c r="J96">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K96">
+        <v>12</v>
+      </c>
+      <c r="L96">
+        <v>15</v>
+      </c>
+      <c r="M96">
+        <v>4</v>
+      </c>
+      <c r="N96">
+        <v>2</v>
+      </c>
+      <c r="O96">
+        <v>1</v>
+      </c>
+      <c r="P96">
+        <v>1</v>
+      </c>
+      <c r="Q96">
+        <v>1</v>
+      </c>
+      <c r="R96">
+        <v>1</v>
+      </c>
+      <c r="S96">
+        <v>436</v>
+      </c>
+      <c r="T96">
+        <v>592</v>
+      </c>
+      <c r="U96">
+        <v>9</v>
+      </c>
+      <c r="V96">
+        <v>12</v>
+      </c>
+      <c r="W96">
+        <v>3</v>
+      </c>
+      <c r="X96">
+        <v>4</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA96">
+        <v>4</v>
+      </c>
+      <c r="AB96">
+        <v>10</v>
+      </c>
+      <c r="AC96">
+        <v>4</v>
+      </c>
+      <c r="AD96">
+        <v>3</v>
+      </c>
+      <c r="AE96">
+        <v>0</v>
+      </c>
+      <c r="AF96">
+        <v>1</v>
+      </c>
+      <c r="AG96">
+        <v>9</v>
+      </c>
+      <c r="AH96">
+        <v>8</v>
+      </c>
+      <c r="AI96">
+        <v>3</v>
+      </c>
+      <c r="AJ96">
+        <v>7</v>
+      </c>
+      <c r="AK96">
+        <v>0.54</v>
+      </c>
+      <c r="AL96">
+        <v>0.93</v>
+      </c>
+      <c r="AM96">
+        <v>0.21</v>
+      </c>
+      <c r="AN96">
+        <v>0.22</v>
+      </c>
+      <c r="AO96">
+        <v>0.76</v>
+      </c>
+      <c r="AP96">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="AQ96">
+        <v>0.68</v>
+      </c>
+      <c r="AR96">
+        <v>0.16</v>
+      </c>
+      <c r="AS96">
+        <v>497</v>
+      </c>
+      <c r="AT96">
+        <v>650</v>
+      </c>
+      <c r="AU96">
+        <v>236</v>
+      </c>
+      <c r="AV96">
+        <v>266</v>
+      </c>
+      <c r="AW96">
+        <v>200</v>
+      </c>
+      <c r="AX96">
+        <v>326</v>
+      </c>
+      <c r="AY96">
+        <v>16</v>
+      </c>
+      <c r="AZ96">
+        <v>18</v>
+      </c>
+      <c r="BA96">
+        <v>7</v>
+      </c>
+      <c r="BB96">
+        <v>4</v>
+      </c>
+      <c r="BC96">
+        <v>19</v>
+      </c>
+      <c r="BD96">
+        <v>14</v>
+      </c>
+      <c r="BE96">
+        <v>23</v>
+      </c>
+      <c r="BF96">
+        <v>26</v>
+      </c>
+      <c r="BG96">
+        <v>2</v>
+      </c>
+      <c r="BH96">
+        <v>2</v>
+      </c>
+      <c r="BI96" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ96" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK96">
+        <v>14</v>
+      </c>
+      <c r="BL96">
+        <v>12</v>
+      </c>
+      <c r="BM96">
+        <v>10</v>
+      </c>
+      <c r="BN96">
+        <v>14</v>
+      </c>
+      <c r="BO96">
+        <v>3</v>
+      </c>
+      <c r="BP96">
+        <v>3</v>
+      </c>
+      <c r="BQ96">
+        <v>13</v>
+      </c>
+      <c r="BR96">
+        <v>17</v>
+      </c>
+      <c r="BS96">
+        <v>2</v>
+      </c>
+      <c r="BT96">
+        <v>4</v>
+      </c>
+      <c r="BU96" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV96" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW96">
+        <v>38</v>
+      </c>
+      <c r="BX96">
+        <v>40</v>
+      </c>
+      <c r="BY96">
+        <v>32</v>
+      </c>
+      <c r="BZ96">
+        <v>25</v>
+      </c>
+      <c r="CA96">
+        <v>6</v>
+      </c>
+      <c r="CB96">
+        <v>15</v>
+      </c>
+      <c r="CC96">
+        <v>7</v>
+      </c>
+      <c r="CD96">
+        <v>4</v>
+      </c>
+      <c r="CE96" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF96" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG96">
+        <v>2</v>
+      </c>
+      <c r="CH96">
+        <v>1</v>
+      </c>
+      <c r="CI96">
+        <v>0</v>
+      </c>
+      <c r="CJ96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:88" ht="25.5">
+      <c r="B97" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D97" t="s">
+        <v>96</v>
+      </c>
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>62</v>
+      </c>
+      <c r="H97">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="I97">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="J97">
+        <v>0.48</v>
+      </c>
+      <c r="K97">
+        <v>17</v>
+      </c>
+      <c r="L97">
+        <v>6</v>
+      </c>
+      <c r="M97">
+        <v>3</v>
+      </c>
+      <c r="N97">
+        <v>2</v>
+      </c>
+      <c r="O97">
+        <v>5</v>
+      </c>
+      <c r="P97">
+        <v>2</v>
+      </c>
+      <c r="Q97">
+        <v>4</v>
+      </c>
+      <c r="R97">
+        <v>1</v>
+      </c>
+      <c r="S97">
+        <v>564</v>
+      </c>
+      <c r="T97">
+        <v>305</v>
+      </c>
+      <c r="U97">
+        <v>14</v>
+      </c>
+      <c r="V97">
+        <v>13</v>
+      </c>
+      <c r="W97">
+        <v>2</v>
+      </c>
+      <c r="X97">
+        <v>3</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA97">
+        <v>11</v>
+      </c>
+      <c r="AB97">
+        <v>4</v>
+      </c>
+      <c r="AC97">
+        <v>3</v>
+      </c>
+      <c r="AD97">
+        <v>0</v>
+      </c>
+      <c r="AE97">
+        <v>0</v>
+      </c>
+      <c r="AF97">
+        <v>0</v>
+      </c>
+      <c r="AG97">
+        <v>14</v>
+      </c>
+      <c r="AH97">
+        <v>4</v>
+      </c>
+      <c r="AI97">
+        <v>3</v>
+      </c>
+      <c r="AJ97">
+        <v>2</v>
+      </c>
+      <c r="AK97">
+        <v>2.16</v>
+      </c>
+      <c r="AL97">
+        <v>0.24</v>
+      </c>
+      <c r="AM97">
+        <v>0.06</v>
+      </c>
+      <c r="AN97">
+        <v>0.24</v>
+      </c>
+      <c r="AO97">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="AP97">
+        <v>0.48</v>
+      </c>
+      <c r="AQ97">
+        <v>1.91</v>
+      </c>
+      <c r="AR97">
+        <v>1.02</v>
+      </c>
+      <c r="AS97">
+        <v>613</v>
+      </c>
+      <c r="AT97">
+        <v>365</v>
+      </c>
+      <c r="AU97">
+        <v>326</v>
+      </c>
+      <c r="AV97">
+        <v>194</v>
+      </c>
+      <c r="AW97">
+        <v>238</v>
+      </c>
+      <c r="AX97">
+        <v>111</v>
+      </c>
+      <c r="AY97">
+        <v>23</v>
+      </c>
+      <c r="AZ97">
+        <v>15</v>
+      </c>
+      <c r="BA97">
+        <v>2</v>
+      </c>
+      <c r="BB97">
+        <v>2</v>
+      </c>
+      <c r="BC97">
+        <v>20</v>
+      </c>
+      <c r="BD97">
+        <v>16</v>
+      </c>
+      <c r="BE97">
+        <v>21</v>
+      </c>
+      <c r="BF97">
+        <v>18</v>
+      </c>
+      <c r="BG97">
+        <v>1</v>
+      </c>
+      <c r="BH97">
+        <v>0</v>
+      </c>
+      <c r="BI97" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ97" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK97">
+        <v>18</v>
+      </c>
+      <c r="BL97">
+        <v>16</v>
+      </c>
+      <c r="BM97">
+        <v>13</v>
+      </c>
+      <c r="BN97">
+        <v>3</v>
+      </c>
+      <c r="BO97">
+        <v>0</v>
+      </c>
+      <c r="BP97">
+        <v>3</v>
+      </c>
+      <c r="BQ97">
+        <v>13</v>
+      </c>
+      <c r="BR97">
+        <v>17</v>
+      </c>
+      <c r="BS97">
+        <v>1</v>
+      </c>
+      <c r="BT97">
+        <v>1</v>
+      </c>
+      <c r="BU97" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV97" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW97">
+        <v>38</v>
+      </c>
+      <c r="BX97">
+        <v>39</v>
+      </c>
+      <c r="BY97">
+        <v>33</v>
+      </c>
+      <c r="BZ97">
+        <v>34</v>
+      </c>
+      <c r="CA97">
+        <v>5</v>
+      </c>
+      <c r="CB97">
+        <v>5</v>
+      </c>
+      <c r="CC97">
+        <v>4</v>
+      </c>
+      <c r="CD97">
+        <v>5</v>
+      </c>
+      <c r="CE97" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF97" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG97">
+        <v>1</v>
+      </c>
+      <c r="CH97">
+        <v>3</v>
+      </c>
+      <c r="CI97">
+        <v>0</v>
+      </c>
+      <c r="CJ97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:88" ht="25.5">
+      <c r="B98" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C98" t="s">
+        <v>119</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <v>2</v>
+      </c>
+      <c r="G98">
+        <v>62</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="I98">
+        <v>1.19</v>
+      </c>
+      <c r="J98">
+        <v>1.94</v>
+      </c>
+      <c r="K98">
+        <v>18</v>
+      </c>
+      <c r="L98">
+        <v>10</v>
+      </c>
+      <c r="M98">
+        <v>6</v>
+      </c>
+      <c r="N98">
+        <v>5</v>
+      </c>
+      <c r="O98">
+        <v>2</v>
+      </c>
+      <c r="P98">
+        <v>4</v>
+      </c>
+      <c r="Q98">
+        <v>2</v>
+      </c>
+      <c r="R98">
+        <v>2</v>
+      </c>
+      <c r="S98">
+        <v>569</v>
+      </c>
+      <c r="T98">
+        <v>320</v>
+      </c>
+      <c r="U98">
+        <v>15</v>
+      </c>
+      <c r="V98">
+        <v>11</v>
+      </c>
+      <c r="W98">
+        <v>6</v>
+      </c>
+      <c r="X98">
+        <v>6</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA98">
+        <v>6</v>
+      </c>
+      <c r="AB98">
+        <v>3</v>
+      </c>
+      <c r="AC98">
+        <v>6</v>
+      </c>
+      <c r="AD98">
+        <v>2</v>
+      </c>
+      <c r="AE98">
+        <v>0</v>
+      </c>
+      <c r="AF98">
+        <v>0</v>
+      </c>
+      <c r="AG98">
+        <v>11</v>
+      </c>
+      <c r="AH98">
+        <v>6</v>
+      </c>
+      <c r="AI98">
+        <v>7</v>
+      </c>
+      <c r="AJ98">
+        <v>4</v>
+      </c>
+      <c r="AK98">
+        <v>1.02</v>
+      </c>
+      <c r="AL98">
+        <v>1.92</v>
+      </c>
+      <c r="AM98">
+        <v>0.17</v>
+      </c>
+      <c r="AN98">
+        <v>0.02</v>
+      </c>
+      <c r="AO98">
+        <v>1.19</v>
+      </c>
+      <c r="AP98">
+        <v>1.94</v>
+      </c>
+      <c r="AQ98">
+        <v>1.22</v>
+      </c>
+      <c r="AR98">
+        <v>2.14</v>
+      </c>
+      <c r="AS98">
+        <v>639</v>
+      </c>
+      <c r="AT98">
+        <v>380</v>
+      </c>
+      <c r="AU98">
+        <v>220</v>
+      </c>
+      <c r="AV98">
+        <v>226</v>
+      </c>
+      <c r="AW98">
+        <v>349</v>
+      </c>
+      <c r="AX98">
+        <v>94</v>
+      </c>
+      <c r="AY98">
+        <v>6</v>
+      </c>
+      <c r="AZ98">
+        <v>27</v>
+      </c>
+      <c r="BA98">
+        <v>2</v>
+      </c>
+      <c r="BB98">
+        <v>1</v>
+      </c>
+      <c r="BC98">
+        <v>19</v>
+      </c>
+      <c r="BD98">
+        <v>9</v>
+      </c>
+      <c r="BE98">
+        <v>36</v>
+      </c>
+      <c r="BF98">
+        <v>24</v>
+      </c>
+      <c r="BG98">
+        <v>3</v>
+      </c>
+      <c r="BH98">
+        <v>3</v>
+      </c>
+      <c r="BI98" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ98" t="s">
+        <v>89</v>
+      </c>
+      <c r="BK98">
+        <v>16</v>
+      </c>
+      <c r="BL98">
+        <v>23</v>
+      </c>
+      <c r="BM98">
+        <v>7</v>
+      </c>
+      <c r="BN98">
+        <v>14</v>
+      </c>
+      <c r="BO98">
+        <v>2</v>
+      </c>
+      <c r="BP98">
+        <v>6</v>
+      </c>
+      <c r="BQ98">
+        <v>16</v>
+      </c>
+      <c r="BR98">
+        <v>30</v>
+      </c>
+      <c r="BS98">
+        <v>3</v>
+      </c>
+      <c r="BT98">
+        <v>5</v>
+      </c>
+      <c r="BU98" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV98" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW98">
+        <v>44</v>
+      </c>
+      <c r="BX98">
+        <v>52</v>
+      </c>
+      <c r="BY98">
+        <v>36</v>
+      </c>
+      <c r="BZ98">
+        <v>49</v>
+      </c>
+      <c r="CA98">
+        <v>8</v>
+      </c>
+      <c r="CB98">
+        <v>3</v>
+      </c>
+      <c r="CC98">
+        <v>9</v>
+      </c>
+      <c r="CD98">
+        <v>12</v>
+      </c>
+      <c r="CE98" t="s">
+        <v>89</v>
+      </c>
+      <c r="CF98" t="s">
+        <v>89</v>
+      </c>
+      <c r="CG98">
+        <v>3</v>
+      </c>
+      <c r="CH98">
+        <v>3</v>
+      </c>
+      <c r="CI98">
+        <v>0</v>
+      </c>
+      <c r="CJ98">
         <v>0</v>
       </c>
     </row>
